--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-13_Data_Migration/BIBS_TestPlan_BRD-13_Data_Migration_v1.2.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-13_Data_Migration/BIBS_TestPlan_BRD-13_Data_Migration_v1.2.xlsx
@@ -16,11 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles and Access" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRS Findings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="10" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Document Control'!$A$4:$F$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Document Control'!$4:$4</definedName>
@@ -28,16 +27,14 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Test Conditions'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Scenarios'!$A$4:$F$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Scenarios'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$R$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$Q$185</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Test Cases'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$J$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$I$71</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Coverage'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Test Data'!$A$4:$E$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Test Data'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Roles and Access'!$A$4:$M$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Roles and Access'!$A$4:$L$60</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Roles and Access'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FRS Findings'!$A$4:$D$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'FRS Findings'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +435,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -751,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E39"/>
+  <dimension ref="B4:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1010,92 +1007,77 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>FRS points raised for the FRS owner; the affected cases assume the proposed resolution</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>2</v>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Legend</t>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>The case ran and the actual result matches the expected result</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>The case ran and the actual result matches the expected result</t>
+          <t>The actual result differs; an issue ID is recorded</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>The actual result differs; a defect ID is recorded</t>
+          <t>The case cannot run (environment, data or an open issue elsewhere)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>The case cannot run (environment, data or a defect elsewhere)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
           <t>Not applicable in this cycle, with the reason in Actual result</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Source: FRS BRD-13 Data Migration. 44 FRs, 23 BRD IDs, 169 test conditions, 9 scenarios, 181 test cases (93 positive, 88 negative).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>Source: FRS BRD-13 (FRS_BRD13_DATA_MIGRATION.md). 44 FRs, 23 BRD IDs, 169 test conditions, 9 scenarios, 181 test cases (93 positive, 88 negative), 0 with an automation reference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>Status starts as Not run. Testers fill Status, Actual result, Tester, Date and Defect ID during execution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="B39" s="20" t="inlineStr">
+          <t>Status starts as Not run. Testers fill Status, Actual result, Tester, Date and Issue ID during execution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -1111,7 +1093,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId9"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -1124,7 +1105,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -1132,134 +1113,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>FRS points raised for the FRS owner; the affected cases assume the proposed resolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="25" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="26" t="inlineStr">
-        <is>
-          <t>FR ID</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>Proposed resolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>TF-DM-01</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>FR-DM-034</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>The Exception-bucket route and its message belong to the Renewal sanitation check PACKAGE_REMAP, which the Renewal FRS does not yet describe; case TC-DM-034.3 checks the bucket only.</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Describe PACKAGE_REMAP (reads the PACKAGE map loaded by R06; unmapped, REJECT or unmatched qualifier to the Exception bucket, worked by the Renewal processing team) with its message in the Renewal FRS, and quote it here in the next issue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>TF-DM-02</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>FR-DM-124</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>The URGENT flag, the priority order and the RA already sent are Renewal candidate attributes; the Renewal FRS does not yet list them, so the cases check them on the worklist only.</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Add the go-live extraction (window to 31 May 2028, URGENT to 31 January 2028, RA already sent from P03) to the Renewal FRS.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:D6"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A5:D506">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Plan BRD-13 Data Migration&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
-    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.2</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1408,6 +1264,20 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>Upload-download</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Message</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1903,7 +1773,7 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Positive, Negative, Boundary, Security-access, Workflow, Report-output, Upload-download</t>
+          <t>Positive, Negative, Boundary, Security-access, Workflow, Report-output, Upload-download, Screen, Message</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1790,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
+          <t>Role code and name (and the SIT/UAT user)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -1992,7 +1862,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>What the system must do, with the exact message text and, for built BRDs, its code</t>
+          <t>What the system must do, with the exact message text and, where the system shows one, its code</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr"/>
@@ -2027,15 +1897,19 @@
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Existing automated test (class#method) that covers the case; blank when none</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr"/>
+          <t>Execution status</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Not run, Pass, Fail, Blocked, N/A</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -2045,19 +1919,15 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Execution status</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
-        <is>
-          <t>Not run, Pass, Fail, Blocked, N/A</t>
-        </is>
-      </c>
+          <t>What happened, filled by the tester</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -2067,12 +1937,12 @@
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>What happened, filled by the tester</t>
+          <t>Who ran the case</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr"/>
@@ -2085,12 +1955,12 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Who ran the case</t>
+          <t>Date of the run</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr"/>
@@ -2103,12 +1973,12 @@
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Issue ID</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Date of the run</t>
+          <t>Issue raised when the case fails</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -2116,17 +1986,17 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Test Cases</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>Defect ID</t>
+          <t>FR / BRD ID</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Defect raised when the case fails</t>
+          <t>FR of the FRS, then BRD requirement ID</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr"/>
@@ -2139,12 +2009,12 @@
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>FR / BRD ID</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>FR of the FRS, then BRD requirement ID</t>
+          <t>FR or BRD ID</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr"/>
@@ -2157,12 +2027,12 @@
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>FR or BRD ID</t>
+          <t>FR title</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr"/>
@@ -2175,12 +2045,12 @@
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Traces</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>FR title</t>
+          <t>BRD IDs of the FR, or FRs of the BRD ID</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
@@ -2193,12 +2063,12 @@
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>Traces</t>
+          <t>Conditions</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>BRD IDs of the FR, or FRs of the BRD ID</t>
+          <t>Test conditions</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr"/>
@@ -2211,12 +2081,12 @@
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>Conditions</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Test conditions</t>
+          <t>Cases where the action succeeds</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr"/>
@@ -2229,12 +2099,12 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Cases where the action succeeds</t>
+          <t>Cases where BIBS refuses the action</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr"/>
@@ -2247,12 +2117,12 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Cases where BIBS refuses the action</t>
+          <t>All cases</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr"/>
@@ -2265,30 +2135,34 @@
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>All cases</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr"/>
+          <t>Covered: at least one positive and one negative case (FR) or one case (BRD ID); GAP otherwise</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>Covered, GAP</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>Automated</t>
+          <t>Data set</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Cases with an automation reference</t>
+          <t>Data set ID</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr"/>
@@ -2296,24 +2170,20 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Covered: at least one positive and one negative case (FR) or one case (BRD ID); GAP otherwise</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>Covered, GAP</t>
-        </is>
-      </c>
+          <t>Short name used in the cases</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -2323,12 +2193,12 @@
       </c>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>Data set</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Data set ID</t>
+          <t>Records and values in the set</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr"/>
@@ -2341,12 +2211,12 @@
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Short name used in the cases</t>
+          <t>Seed data set that provides it, or how the tester prepares it; non-production data is masked</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr"/>
@@ -2359,12 +2229,12 @@
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Cases</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Records and values in the set</t>
+          <t>Number of cases that use it</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr"/>
@@ -2372,17 +2242,17 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Roles and Access</t>
         </is>
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Case ID</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Access case ID: AC-&lt;code&gt;-&lt;nn&gt;.&lt;n&gt;</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -2390,17 +2260,17 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Roles and Access</t>
         </is>
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>Cases</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Number of cases that use it</t>
+          <t>Screen or action checked</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr"/>
@@ -2413,12 +2283,12 @@
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>Case ID</t>
+          <t>Screen (menu path)</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Access case ID: AC-&lt;code&gt;-&lt;nn&gt;.&lt;n&gt;</t>
+          <t>Where it is done</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr"/>
@@ -2431,12 +2301,12 @@
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Permission</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Screen or action checked</t>
+          <t>BIBS permission that grants it</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr"/>
@@ -2449,12 +2319,12 @@
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
-          <t>Screen (menu path)</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Where it is done</t>
+          <t>Role tested (log in as a user who holds only this role)</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr"/>
@@ -2467,15 +2337,19 @@
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>BIBS permission that grants it</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr"/>
+          <t>Expected access</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Allowed, Denied</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
@@ -2485,12 +2359,12 @@
       </c>
       <c r="B60" s="23" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Expected result</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Role tested (log in as a user who holds only this role)</t>
+          <t>What the user sees</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr"/>
@@ -2503,17 +2377,17 @@
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Expected access</t>
+          <t>Execution status</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Allowed, Denied</t>
+          <t>Not run, Pass, Fail, Blocked, N/A</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2399,12 @@
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>Expected result</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>What the user sees</t>
+          <t>Filled by the tester</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr"/>
@@ -2543,12 +2417,12 @@
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Existing automated test, if any</t>
+          <t>Who ran the case</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr"/>
@@ -2561,19 +2435,15 @@
       </c>
       <c r="B64" s="23" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Execution status</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>Not run, Pass, Fail, Blocked, N/A</t>
-        </is>
-      </c>
+          <t>Date of the run</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -2583,144 +2453,18 @@
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Issue ID</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Filled by the tester</t>
+          <t>Issue raised when the case fails</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr"/>
     </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B66" s="23" t="inlineStr">
-        <is>
-          <t>Tester</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="inlineStr">
-        <is>
-          <t>Who ran the case</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B67" s="22" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t>Date of the run</t>
-        </is>
-      </c>
-      <c r="D67" s="12" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B68" s="23" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
-        <is>
-          <t>Defect raised when the case fails</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>Finding ID</t>
-        </is>
-      </c>
-      <c r="D69" s="12" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B70" s="23" t="inlineStr">
-        <is>
-          <t>FR ID</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>FR concerned</t>
-        </is>
-      </c>
-      <c r="D70" s="14" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="12" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B71" s="22" t="inlineStr">
-        <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="C71" s="12" t="inlineStr">
-        <is>
-          <t>Ambiguous or untestable point found while writing the cases</t>
-        </is>
-      </c>
-      <c r="D71" s="12" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B72" s="23" t="inlineStr">
-        <is>
-          <t>Proposed resolution</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>What the test team proposes to the FRS owner</t>
-        </is>
-      </c>
-      <c r="D72" s="14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D72"/>
+  <autoFilter ref="A4:D65"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -8805,7 +8549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R185"/>
+  <dimension ref="A1:Q185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8820,12 +8564,11 @@
     <col width="52" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -8860,7 +8603,6 @@
       <c r="O3" s="25" t="n"/>
       <c r="P3" s="25" t="n"/>
       <c r="Q3" s="25" t="n"/>
-      <c r="R3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -8925,32 +8667,27 @@
       </c>
       <c r="M4" s="26" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="N4" s="26" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="O4" s="26" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="P4" s="26" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="26" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="26" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
+          <t>Issue ID</t>
         </is>
       </c>
     </row>
@@ -9016,16 +8753,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M5" s="12" t="inlineStr"/>
-      <c r="N5" s="27" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N5" s="12" t="n"/>
       <c r="O5" s="12" t="n"/>
-      <c r="P5" s="12" t="n"/>
-      <c r="Q5" s="28" t="n"/>
-      <c r="R5" s="12" t="n"/>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -9089,16 +8825,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="27" t="inlineStr">
+      <c r="M6" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N6" s="12" t="n"/>
       <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="28" t="n"/>
-      <c r="R6" s="12" t="n"/>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -9161,16 +8896,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N7" s="12" t="n"/>
       <c r="O7" s="12" t="n"/>
-      <c r="P7" s="12" t="n"/>
-      <c r="Q7" s="28" t="n"/>
-      <c r="R7" s="12" t="n"/>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -9235,16 +8969,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="27" t="inlineStr">
+      <c r="M8" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N8" s="12" t="n"/>
       <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
-      <c r="Q8" s="28" t="n"/>
-      <c r="R8" s="12" t="n"/>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -9308,16 +9041,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="27" t="inlineStr">
+      <c r="M9" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N9" s="12" t="n"/>
       <c r="O9" s="12" t="n"/>
-      <c r="P9" s="12" t="n"/>
-      <c r="Q9" s="28" t="n"/>
-      <c r="R9" s="12" t="n"/>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -9382,16 +9114,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="27" t="inlineStr">
+      <c r="M10" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N10" s="12" t="n"/>
       <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
-      <c r="Q10" s="28" t="n"/>
-      <c r="R10" s="12" t="n"/>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -9455,16 +9186,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="27" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N11" s="12" t="n"/>
       <c r="O11" s="12" t="n"/>
-      <c r="P11" s="12" t="n"/>
-      <c r="Q11" s="28" t="n"/>
-      <c r="R11" s="12" t="n"/>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -9529,16 +9259,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="27" t="inlineStr">
+      <c r="M12" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N12" s="12" t="n"/>
       <c r="O12" s="12" t="n"/>
-      <c r="P12" s="12" t="n"/>
-      <c r="Q12" s="28" t="n"/>
-      <c r="R12" s="12" t="n"/>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -9601,16 +9330,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="27" t="inlineStr">
+      <c r="M13" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N13" s="12" t="n"/>
       <c r="O13" s="12" t="n"/>
-      <c r="P13" s="12" t="n"/>
-      <c r="Q13" s="28" t="n"/>
-      <c r="R13" s="12" t="n"/>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -9673,16 +9401,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="27" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N14" s="12" t="n"/>
       <c r="O14" s="12" t="n"/>
-      <c r="P14" s="12" t="n"/>
-      <c r="Q14" s="28" t="n"/>
-      <c r="R14" s="12" t="n"/>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -9746,16 +9473,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="27" t="inlineStr">
+      <c r="M15" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N15" s="12" t="n"/>
       <c r="O15" s="12" t="n"/>
-      <c r="P15" s="12" t="n"/>
-      <c r="Q15" s="28" t="n"/>
-      <c r="R15" s="12" t="n"/>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -9820,16 +9546,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="27" t="inlineStr">
+      <c r="M16" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N16" s="12" t="n"/>
       <c r="O16" s="12" t="n"/>
-      <c r="P16" s="12" t="n"/>
-      <c r="Q16" s="28" t="n"/>
-      <c r="R16" s="12" t="n"/>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -9893,16 +9618,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="27" t="inlineStr">
+      <c r="M17" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N17" s="12" t="n"/>
       <c r="O17" s="12" t="n"/>
-      <c r="P17" s="12" t="n"/>
-      <c r="Q17" s="28" t="n"/>
-      <c r="R17" s="12" t="n"/>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -9965,16 +9689,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M18" s="12" t="inlineStr"/>
-      <c r="N18" s="27" t="inlineStr">
+      <c r="M18" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N18" s="12" t="n"/>
       <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
-      <c r="Q18" s="28" t="n"/>
-      <c r="R18" s="12" t="n"/>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -10037,16 +9760,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="27" t="inlineStr">
+      <c r="M19" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N19" s="12" t="n"/>
       <c r="O19" s="12" t="n"/>
-      <c r="P19" s="12" t="n"/>
-      <c r="Q19" s="28" t="n"/>
-      <c r="R19" s="12" t="n"/>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -10110,16 +9832,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M20" s="12" t="inlineStr"/>
-      <c r="N20" s="27" t="inlineStr">
+      <c r="M20" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N20" s="12" t="n"/>
       <c r="O20" s="12" t="n"/>
-      <c r="P20" s="12" t="n"/>
-      <c r="Q20" s="28" t="n"/>
-      <c r="R20" s="12" t="n"/>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -10169,12 +9890,12 @@
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>1. Upload a file edited after the control file was made; then a file with column open_balance renamed.</t>
+          <t>1. Upload a file edited after the control file was made; then a file with column open_balance renamed OpenBal.</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>Both REJECTED. The second check shows "The file columns do not match layout version 1: missing open_balance, extra open_bal".
+          <t>Both REJECTED. The second check shows "The file columns do not match layout version 1: missing open_balance, extra OpenBal".
 Message "The file does not match the checksum in the control file".</t>
         </is>
       </c>
@@ -10183,16 +9904,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="27" t="inlineStr">
+      <c r="M21" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N21" s="12" t="n"/>
       <c r="O21" s="12" t="n"/>
-      <c r="P21" s="12" t="n"/>
-      <c r="Q21" s="28" t="n"/>
-      <c r="R21" s="12" t="n"/>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -10256,16 +9976,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M22" s="12" t="inlineStr"/>
-      <c r="N22" s="27" t="inlineStr">
+      <c r="M22" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N22" s="12" t="n"/>
       <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
-      <c r="Q22" s="28" t="n"/>
-      <c r="R22" s="12" t="n"/>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -10330,16 +10049,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M23" s="12" t="inlineStr"/>
-      <c r="N23" s="27" t="inlineStr">
+      <c r="M23" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N23" s="12" t="n"/>
       <c r="O23" s="12" t="n"/>
-      <c r="P23" s="12" t="n"/>
-      <c r="Q23" s="28" t="n"/>
-      <c r="R23" s="12" t="n"/>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -10402,16 +10120,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M24" s="12" t="inlineStr"/>
-      <c r="N24" s="27" t="inlineStr">
+      <c r="M24" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N24" s="12" t="n"/>
       <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
-      <c r="Q24" s="28" t="n"/>
-      <c r="R24" s="12" t="n"/>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -10475,16 +10192,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M25" s="12" t="inlineStr"/>
-      <c r="N25" s="27" t="inlineStr">
+      <c r="M25" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N25" s="12" t="n"/>
       <c r="O25" s="12" t="n"/>
-      <c r="P25" s="12" t="n"/>
-      <c r="Q25" s="28" t="n"/>
-      <c r="R25" s="12" t="n"/>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -10548,16 +10264,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M26" s="12" t="inlineStr"/>
-      <c r="N26" s="27" t="inlineStr">
+      <c r="M26" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N26" s="12" t="n"/>
       <c r="O26" s="12" t="n"/>
-      <c r="P26" s="12" t="n"/>
-      <c r="Q26" s="28" t="n"/>
-      <c r="R26" s="12" t="n"/>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -10621,16 +10336,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M27" s="12" t="inlineStr"/>
-      <c r="N27" s="27" t="inlineStr">
+      <c r="M27" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N27" s="12" t="n"/>
       <c r="O27" s="12" t="n"/>
-      <c r="P27" s="12" t="n"/>
-      <c r="Q27" s="28" t="n"/>
-      <c r="R27" s="12" t="n"/>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -10695,16 +10409,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M28" s="12" t="inlineStr"/>
-      <c r="N28" s="27" t="inlineStr">
+      <c r="M28" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N28" s="12" t="n"/>
       <c r="O28" s="12" t="n"/>
-      <c r="P28" s="12" t="n"/>
-      <c r="Q28" s="28" t="n"/>
-      <c r="R28" s="12" t="n"/>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -10768,16 +10481,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M29" s="12" t="inlineStr"/>
-      <c r="N29" s="27" t="inlineStr">
+      <c r="M29" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N29" s="12" t="n"/>
       <c r="O29" s="12" t="n"/>
-      <c r="P29" s="12" t="n"/>
-      <c r="Q29" s="28" t="n"/>
-      <c r="R29" s="12" t="n"/>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -10840,16 +10552,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M30" s="12" t="inlineStr"/>
-      <c r="N30" s="27" t="inlineStr">
+      <c r="M30" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N30" s="12" t="n"/>
       <c r="O30" s="12" t="n"/>
-      <c r="P30" s="12" t="n"/>
-      <c r="Q30" s="28" t="n"/>
-      <c r="R30" s="12" t="n"/>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -10913,16 +10624,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M31" s="12" t="inlineStr"/>
-      <c r="N31" s="27" t="inlineStr">
+      <c r="M31" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N31" s="12" t="n"/>
       <c r="O31" s="12" t="n"/>
-      <c r="P31" s="12" t="n"/>
-      <c r="Q31" s="28" t="n"/>
-      <c r="R31" s="12" t="n"/>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -10985,16 +10695,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M32" s="12" t="inlineStr"/>
-      <c r="N32" s="27" t="inlineStr">
+      <c r="M32" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N32" s="12" t="n"/>
       <c r="O32" s="12" t="n"/>
-      <c r="P32" s="12" t="n"/>
-      <c r="Q32" s="28" t="n"/>
-      <c r="R32" s="12" t="n"/>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -11057,16 +10766,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M33" s="12" t="inlineStr"/>
-      <c r="N33" s="27" t="inlineStr">
+      <c r="M33" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N33" s="12" t="n"/>
       <c r="O33" s="12" t="n"/>
-      <c r="P33" s="12" t="n"/>
-      <c r="Q33" s="28" t="n"/>
-      <c r="R33" s="12" t="n"/>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -11130,16 +10838,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M34" s="12" t="inlineStr"/>
-      <c r="N34" s="27" t="inlineStr">
+      <c r="M34" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N34" s="12" t="n"/>
       <c r="O34" s="12" t="n"/>
-      <c r="P34" s="12" t="n"/>
-      <c r="Q34" s="28" t="n"/>
-      <c r="R34" s="12" t="n"/>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -11203,16 +10910,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M35" s="12" t="inlineStr"/>
-      <c r="N35" s="27" t="inlineStr">
+      <c r="M35" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N35" s="12" t="n"/>
       <c r="O35" s="12" t="n"/>
-      <c r="P35" s="12" t="n"/>
-      <c r="Q35" s="28" t="n"/>
-      <c r="R35" s="12" t="n"/>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -11275,16 +10981,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M36" s="12" t="inlineStr"/>
-      <c r="N36" s="27" t="inlineStr">
+      <c r="M36" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N36" s="12" t="n"/>
       <c r="O36" s="12" t="n"/>
-      <c r="P36" s="12" t="n"/>
-      <c r="Q36" s="28" t="n"/>
-      <c r="R36" s="12" t="n"/>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -11348,16 +11053,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M37" s="12" t="inlineStr"/>
-      <c r="N37" s="27" t="inlineStr">
+      <c r="M37" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N37" s="12" t="n"/>
       <c r="O37" s="12" t="n"/>
-      <c r="P37" s="12" t="n"/>
-      <c r="Q37" s="28" t="n"/>
-      <c r="R37" s="12" t="n"/>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -11421,16 +11125,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M38" s="12" t="inlineStr"/>
-      <c r="N38" s="27" t="inlineStr">
+      <c r="M38" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N38" s="12" t="n"/>
       <c r="O38" s="12" t="n"/>
-      <c r="P38" s="12" t="n"/>
-      <c r="Q38" s="28" t="n"/>
-      <c r="R38" s="12" t="n"/>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -11493,16 +11196,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M39" s="12" t="inlineStr"/>
-      <c r="N39" s="27" t="inlineStr">
+      <c r="M39" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N39" s="12" t="n"/>
       <c r="O39" s="12" t="n"/>
-      <c r="P39" s="12" t="n"/>
-      <c r="Q39" s="28" t="n"/>
-      <c r="R39" s="12" t="n"/>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -11565,16 +11267,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M40" s="12" t="inlineStr"/>
-      <c r="N40" s="27" t="inlineStr">
+      <c r="M40" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
-      <c r="P40" s="12" t="n"/>
-      <c r="Q40" s="28" t="n"/>
-      <c r="R40" s="12" t="n"/>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -11637,16 +11338,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M41" s="12" t="inlineStr"/>
-      <c r="N41" s="27" t="inlineStr">
+      <c r="M41" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N41" s="12" t="n"/>
       <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
-      <c r="Q41" s="28" t="n"/>
-      <c r="R41" s="12" t="n"/>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -11710,16 +11410,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M42" s="12" t="inlineStr"/>
-      <c r="N42" s="27" t="inlineStr">
+      <c r="M42" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N42" s="12" t="n"/>
       <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
-      <c r="Q42" s="28" t="n"/>
-      <c r="R42" s="12" t="n"/>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -11784,16 +11483,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M43" s="12" t="inlineStr"/>
-      <c r="N43" s="27" t="inlineStr">
+      <c r="M43" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N43" s="12" t="n"/>
       <c r="O43" s="12" t="n"/>
-      <c r="P43" s="12" t="n"/>
-      <c r="Q43" s="28" t="n"/>
-      <c r="R43" s="12" t="n"/>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -11856,16 +11554,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M44" s="12" t="inlineStr"/>
-      <c r="N44" s="27" t="inlineStr">
+      <c r="M44" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N44" s="12" t="n"/>
       <c r="O44" s="12" t="n"/>
-      <c r="P44" s="12" t="n"/>
-      <c r="Q44" s="28" t="n"/>
-      <c r="R44" s="12" t="n"/>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -11928,16 +11625,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M45" s="12" t="inlineStr"/>
-      <c r="N45" s="27" t="inlineStr">
+      <c r="M45" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N45" s="12" t="n"/>
       <c r="O45" s="12" t="n"/>
-      <c r="P45" s="12" t="n"/>
-      <c r="Q45" s="28" t="n"/>
-      <c r="R45" s="12" t="n"/>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -12001,16 +11697,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M46" s="12" t="inlineStr"/>
-      <c r="N46" s="27" t="inlineStr">
+      <c r="M46" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N46" s="12" t="n"/>
       <c r="O46" s="12" t="n"/>
-      <c r="P46" s="12" t="n"/>
-      <c r="Q46" s="28" t="n"/>
-      <c r="R46" s="12" t="n"/>
+      <c r="P46" s="28" t="n"/>
+      <c r="Q46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -12075,16 +11770,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M47" s="12" t="inlineStr"/>
-      <c r="N47" s="27" t="inlineStr">
+      <c r="M47" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N47" s="12" t="n"/>
       <c r="O47" s="12" t="n"/>
-      <c r="P47" s="12" t="n"/>
-      <c r="Q47" s="28" t="n"/>
-      <c r="R47" s="12" t="n"/>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -12147,16 +11841,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M48" s="12" t="inlineStr"/>
-      <c r="N48" s="27" t="inlineStr">
+      <c r="M48" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N48" s="12" t="n"/>
       <c r="O48" s="12" t="n"/>
-      <c r="P48" s="12" t="n"/>
-      <c r="Q48" s="28" t="n"/>
-      <c r="R48" s="12" t="n"/>
+      <c r="P48" s="28" t="n"/>
+      <c r="Q48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -12219,16 +11912,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M49" s="12" t="inlineStr"/>
-      <c r="N49" s="27" t="inlineStr">
+      <c r="M49" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N49" s="12" t="n"/>
       <c r="O49" s="12" t="n"/>
-      <c r="P49" s="12" t="n"/>
-      <c r="Q49" s="28" t="n"/>
-      <c r="R49" s="12" t="n"/>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -12293,16 +11985,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M50" s="12" t="inlineStr"/>
-      <c r="N50" s="27" t="inlineStr">
+      <c r="M50" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N50" s="12" t="n"/>
       <c r="O50" s="12" t="n"/>
-      <c r="P50" s="12" t="n"/>
-      <c r="Q50" s="28" t="n"/>
-      <c r="R50" s="12" t="n"/>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -12365,16 +12056,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M51" s="12" t="inlineStr"/>
-      <c r="N51" s="27" t="inlineStr">
+      <c r="M51" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N51" s="12" t="n"/>
       <c r="O51" s="12" t="n"/>
-      <c r="P51" s="12" t="n"/>
-      <c r="Q51" s="28" t="n"/>
-      <c r="R51" s="12" t="n"/>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -12437,16 +12127,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M52" s="12" t="inlineStr"/>
-      <c r="N52" s="27" t="inlineStr">
+      <c r="M52" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N52" s="12" t="n"/>
       <c r="O52" s="12" t="n"/>
-      <c r="P52" s="12" t="n"/>
-      <c r="Q52" s="28" t="n"/>
-      <c r="R52" s="12" t="n"/>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -12509,16 +12198,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M53" s="12" t="inlineStr"/>
-      <c r="N53" s="27" t="inlineStr">
+      <c r="M53" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N53" s="12" t="n"/>
       <c r="O53" s="12" t="n"/>
-      <c r="P53" s="12" t="n"/>
-      <c r="Q53" s="28" t="n"/>
-      <c r="R53" s="12" t="n"/>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -12582,16 +12270,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M54" s="12" t="inlineStr"/>
-      <c r="N54" s="27" t="inlineStr">
+      <c r="M54" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N54" s="12" t="n"/>
       <c r="O54" s="12" t="n"/>
-      <c r="P54" s="12" t="n"/>
-      <c r="Q54" s="28" t="n"/>
-      <c r="R54" s="12" t="n"/>
+      <c r="P54" s="28" t="n"/>
+      <c r="Q54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -12655,16 +12342,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M55" s="12" t="inlineStr"/>
-      <c r="N55" s="27" t="inlineStr">
+      <c r="M55" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N55" s="12" t="n"/>
       <c r="O55" s="12" t="n"/>
-      <c r="P55" s="12" t="n"/>
-      <c r="Q55" s="28" t="n"/>
-      <c r="R55" s="12" t="n"/>
+      <c r="P55" s="28" t="n"/>
+      <c r="Q55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -12728,16 +12414,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M56" s="12" t="inlineStr"/>
-      <c r="N56" s="27" t="inlineStr">
+      <c r="M56" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N56" s="12" t="n"/>
       <c r="O56" s="12" t="n"/>
-      <c r="P56" s="12" t="n"/>
-      <c r="Q56" s="28" t="n"/>
-      <c r="R56" s="12" t="n"/>
+      <c r="P56" s="28" t="n"/>
+      <c r="Q56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -12800,16 +12485,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M57" s="12" t="inlineStr"/>
-      <c r="N57" s="27" t="inlineStr">
+      <c r="M57" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N57" s="12" t="n"/>
       <c r="O57" s="12" t="n"/>
-      <c r="P57" s="12" t="n"/>
-      <c r="Q57" s="28" t="n"/>
-      <c r="R57" s="12" t="n"/>
+      <c r="P57" s="28" t="n"/>
+      <c r="Q57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -12874,16 +12558,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M58" s="12" t="inlineStr"/>
-      <c r="N58" s="27" t="inlineStr">
+      <c r="M58" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N58" s="12" t="n"/>
       <c r="O58" s="12" t="n"/>
-      <c r="P58" s="12" t="n"/>
-      <c r="Q58" s="28" t="n"/>
-      <c r="R58" s="12" t="n"/>
+      <c r="P58" s="28" t="n"/>
+      <c r="Q58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -12946,16 +12629,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M59" s="12" t="inlineStr"/>
-      <c r="N59" s="27" t="inlineStr">
+      <c r="M59" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N59" s="12" t="n"/>
       <c r="O59" s="12" t="n"/>
-      <c r="P59" s="12" t="n"/>
-      <c r="Q59" s="28" t="n"/>
-      <c r="R59" s="12" t="n"/>
+      <c r="P59" s="28" t="n"/>
+      <c r="Q59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -13019,16 +12701,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M60" s="12" t="inlineStr"/>
-      <c r="N60" s="27" t="inlineStr">
+      <c r="M60" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N60" s="12" t="n"/>
       <c r="O60" s="12" t="n"/>
-      <c r="P60" s="12" t="n"/>
-      <c r="Q60" s="28" t="n"/>
-      <c r="R60" s="12" t="n"/>
+      <c r="P60" s="28" t="n"/>
+      <c r="Q60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -13093,16 +12774,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M61" s="12" t="inlineStr"/>
-      <c r="N61" s="27" t="inlineStr">
+      <c r="M61" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N61" s="12" t="n"/>
       <c r="O61" s="12" t="n"/>
-      <c r="P61" s="12" t="n"/>
-      <c r="Q61" s="28" t="n"/>
-      <c r="R61" s="12" t="n"/>
+      <c r="P61" s="28" t="n"/>
+      <c r="Q61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -13165,16 +12845,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M62" s="12" t="inlineStr"/>
-      <c r="N62" s="27" t="inlineStr">
+      <c r="M62" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N62" s="12" t="n"/>
       <c r="O62" s="12" t="n"/>
-      <c r="P62" s="12" t="n"/>
-      <c r="Q62" s="28" t="n"/>
-      <c r="R62" s="12" t="n"/>
+      <c r="P62" s="28" t="n"/>
+      <c r="Q62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -13238,16 +12917,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M63" s="12" t="inlineStr"/>
-      <c r="N63" s="27" t="inlineStr">
+      <c r="M63" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N63" s="12" t="n"/>
       <c r="O63" s="12" t="n"/>
-      <c r="P63" s="12" t="n"/>
-      <c r="Q63" s="28" t="n"/>
-      <c r="R63" s="12" t="n"/>
+      <c r="P63" s="28" t="n"/>
+      <c r="Q63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
@@ -13312,16 +12990,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M64" s="12" t="inlineStr"/>
-      <c r="N64" s="27" t="inlineStr">
+      <c r="M64" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N64" s="12" t="n"/>
       <c r="O64" s="12" t="n"/>
-      <c r="P64" s="12" t="n"/>
-      <c r="Q64" s="28" t="n"/>
-      <c r="R64" s="12" t="n"/>
+      <c r="P64" s="28" t="n"/>
+      <c r="Q64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -13385,16 +13062,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M65" s="12" t="inlineStr"/>
-      <c r="N65" s="27" t="inlineStr">
+      <c r="M65" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N65" s="12" t="n"/>
       <c r="O65" s="12" t="n"/>
-      <c r="P65" s="12" t="n"/>
-      <c r="Q65" s="28" t="n"/>
-      <c r="R65" s="12" t="n"/>
+      <c r="P65" s="28" t="n"/>
+      <c r="Q65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
@@ -13458,16 +13134,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M66" s="12" t="inlineStr"/>
-      <c r="N66" s="27" t="inlineStr">
+      <c r="M66" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N66" s="12" t="n"/>
       <c r="O66" s="12" t="n"/>
-      <c r="P66" s="12" t="n"/>
-      <c r="Q66" s="28" t="n"/>
-      <c r="R66" s="12" t="n"/>
+      <c r="P66" s="28" t="n"/>
+      <c r="Q66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
@@ -13530,16 +13205,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M67" s="12" t="inlineStr"/>
-      <c r="N67" s="27" t="inlineStr">
+      <c r="M67" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N67" s="12" t="n"/>
       <c r="O67" s="12" t="n"/>
-      <c r="P67" s="12" t="n"/>
-      <c r="Q67" s="28" t="n"/>
-      <c r="R67" s="12" t="n"/>
+      <c r="P67" s="28" t="n"/>
+      <c r="Q67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
@@ -13602,16 +13276,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M68" s="12" t="inlineStr"/>
-      <c r="N68" s="27" t="inlineStr">
+      <c r="M68" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N68" s="12" t="n"/>
       <c r="O68" s="12" t="n"/>
-      <c r="P68" s="12" t="n"/>
-      <c r="Q68" s="28" t="n"/>
-      <c r="R68" s="12" t="n"/>
+      <c r="P68" s="28" t="n"/>
+      <c r="Q68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
@@ -13676,16 +13349,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M69" s="12" t="inlineStr"/>
-      <c r="N69" s="27" t="inlineStr">
+      <c r="M69" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N69" s="12" t="n"/>
       <c r="O69" s="12" t="n"/>
-      <c r="P69" s="12" t="n"/>
-      <c r="Q69" s="28" t="n"/>
-      <c r="R69" s="12" t="n"/>
+      <c r="P69" s="28" t="n"/>
+      <c r="Q69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
@@ -13750,16 +13422,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M70" s="12" t="inlineStr"/>
-      <c r="N70" s="27" t="inlineStr">
+      <c r="M70" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N70" s="12" t="n"/>
       <c r="O70" s="12" t="n"/>
-      <c r="P70" s="12" t="n"/>
-      <c r="Q70" s="28" t="n"/>
-      <c r="R70" s="12" t="n"/>
+      <c r="P70" s="28" t="n"/>
+      <c r="Q70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
@@ -13824,16 +13495,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M71" s="12" t="inlineStr"/>
-      <c r="N71" s="27" t="inlineStr">
+      <c r="M71" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N71" s="12" t="n"/>
       <c r="O71" s="12" t="n"/>
-      <c r="P71" s="12" t="n"/>
-      <c r="Q71" s="28" t="n"/>
-      <c r="R71" s="12" t="n"/>
+      <c r="P71" s="28" t="n"/>
+      <c r="Q71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -13896,16 +13566,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M72" s="12" t="inlineStr"/>
-      <c r="N72" s="27" t="inlineStr">
+      <c r="M72" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N72" s="12" t="n"/>
       <c r="O72" s="12" t="n"/>
-      <c r="P72" s="12" t="n"/>
-      <c r="Q72" s="28" t="n"/>
-      <c r="R72" s="12" t="n"/>
+      <c r="P72" s="28" t="n"/>
+      <c r="Q72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
@@ -13969,16 +13638,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M73" s="12" t="inlineStr"/>
-      <c r="N73" s="27" t="inlineStr">
+      <c r="M73" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N73" s="12" t="n"/>
       <c r="O73" s="12" t="n"/>
-      <c r="P73" s="12" t="n"/>
-      <c r="Q73" s="28" t="n"/>
-      <c r="R73" s="12" t="n"/>
+      <c r="P73" s="28" t="n"/>
+      <c r="Q73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
@@ -14041,16 +13709,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M74" s="12" t="inlineStr"/>
-      <c r="N74" s="27" t="inlineStr">
+      <c r="M74" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N74" s="12" t="n"/>
       <c r="O74" s="12" t="n"/>
-      <c r="P74" s="12" t="n"/>
-      <c r="Q74" s="28" t="n"/>
-      <c r="R74" s="12" t="n"/>
+      <c r="P74" s="28" t="n"/>
+      <c r="Q74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
@@ -14113,16 +13780,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M75" s="12" t="inlineStr"/>
-      <c r="N75" s="27" t="inlineStr">
+      <c r="M75" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N75" s="12" t="n"/>
       <c r="O75" s="12" t="n"/>
-      <c r="P75" s="12" t="n"/>
-      <c r="Q75" s="28" t="n"/>
-      <c r="R75" s="12" t="n"/>
+      <c r="P75" s="28" t="n"/>
+      <c r="Q75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
@@ -14186,16 +13852,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M76" s="12" t="inlineStr"/>
-      <c r="N76" s="27" t="inlineStr">
+      <c r="M76" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N76" s="12" t="n"/>
       <c r="O76" s="12" t="n"/>
-      <c r="P76" s="12" t="n"/>
-      <c r="Q76" s="28" t="n"/>
-      <c r="R76" s="12" t="n"/>
+      <c r="P76" s="28" t="n"/>
+      <c r="Q76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
@@ -14258,16 +13923,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M77" s="12" t="inlineStr"/>
-      <c r="N77" s="27" t="inlineStr">
+      <c r="M77" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N77" s="12" t="n"/>
       <c r="O77" s="12" t="n"/>
-      <c r="P77" s="12" t="n"/>
-      <c r="Q77" s="28" t="n"/>
-      <c r="R77" s="12" t="n"/>
+      <c r="P77" s="28" t="n"/>
+      <c r="Q77" s="12" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
@@ -14330,16 +13994,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M78" s="12" t="inlineStr"/>
-      <c r="N78" s="27" t="inlineStr">
+      <c r="M78" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N78" s="12" t="n"/>
       <c r="O78" s="12" t="n"/>
-      <c r="P78" s="12" t="n"/>
-      <c r="Q78" s="28" t="n"/>
-      <c r="R78" s="12" t="n"/>
+      <c r="P78" s="28" t="n"/>
+      <c r="Q78" s="12" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
@@ -14402,16 +14065,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M79" s="12" t="inlineStr"/>
-      <c r="N79" s="27" t="inlineStr">
+      <c r="M79" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N79" s="12" t="n"/>
       <c r="O79" s="12" t="n"/>
-      <c r="P79" s="12" t="n"/>
-      <c r="Q79" s="28" t="n"/>
-      <c r="R79" s="12" t="n"/>
+      <c r="P79" s="28" t="n"/>
+      <c r="Q79" s="12" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
@@ -14474,16 +14136,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M80" s="12" t="inlineStr"/>
-      <c r="N80" s="27" t="inlineStr">
+      <c r="M80" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N80" s="12" t="n"/>
       <c r="O80" s="12" t="n"/>
-      <c r="P80" s="12" t="n"/>
-      <c r="Q80" s="28" t="n"/>
-      <c r="R80" s="12" t="n"/>
+      <c r="P80" s="28" t="n"/>
+      <c r="Q80" s="12" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
@@ -14547,16 +14208,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M81" s="12" t="inlineStr"/>
-      <c r="N81" s="27" t="inlineStr">
+      <c r="M81" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N81" s="12" t="n"/>
       <c r="O81" s="12" t="n"/>
-      <c r="P81" s="12" t="n"/>
-      <c r="Q81" s="28" t="n"/>
-      <c r="R81" s="12" t="n"/>
+      <c r="P81" s="28" t="n"/>
+      <c r="Q81" s="12" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
@@ -14619,16 +14279,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M82" s="12" t="inlineStr"/>
-      <c r="N82" s="27" t="inlineStr">
+      <c r="M82" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N82" s="12" t="n"/>
       <c r="O82" s="12" t="n"/>
-      <c r="P82" s="12" t="n"/>
-      <c r="Q82" s="28" t="n"/>
-      <c r="R82" s="12" t="n"/>
+      <c r="P82" s="28" t="n"/>
+      <c r="Q82" s="12" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
@@ -14691,16 +14350,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M83" s="12" t="inlineStr"/>
-      <c r="N83" s="27" t="inlineStr">
+      <c r="M83" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N83" s="12" t="n"/>
       <c r="O83" s="12" t="n"/>
-      <c r="P83" s="12" t="n"/>
-      <c r="Q83" s="28" t="n"/>
-      <c r="R83" s="12" t="n"/>
+      <c r="P83" s="28" t="n"/>
+      <c r="Q83" s="12" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
@@ -14764,16 +14422,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M84" s="12" t="inlineStr"/>
-      <c r="N84" s="27" t="inlineStr">
+      <c r="M84" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N84" s="12" t="n"/>
       <c r="O84" s="12" t="n"/>
-      <c r="P84" s="12" t="n"/>
-      <c r="Q84" s="28" t="n"/>
-      <c r="R84" s="12" t="n"/>
+      <c r="P84" s="28" t="n"/>
+      <c r="Q84" s="12" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
@@ -14837,16 +14494,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M85" s="12" t="inlineStr"/>
-      <c r="N85" s="27" t="inlineStr">
+      <c r="M85" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N85" s="12" t="n"/>
       <c r="O85" s="12" t="n"/>
-      <c r="P85" s="12" t="n"/>
-      <c r="Q85" s="28" t="n"/>
-      <c r="R85" s="12" t="n"/>
+      <c r="P85" s="28" t="n"/>
+      <c r="Q85" s="12" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
@@ -14909,16 +14565,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M86" s="12" t="inlineStr"/>
-      <c r="N86" s="27" t="inlineStr">
+      <c r="M86" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N86" s="12" t="n"/>
       <c r="O86" s="12" t="n"/>
-      <c r="P86" s="12" t="n"/>
-      <c r="Q86" s="28" t="n"/>
-      <c r="R86" s="12" t="n"/>
+      <c r="P86" s="28" t="n"/>
+      <c r="Q86" s="12" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
@@ -14981,16 +14636,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M87" s="12" t="inlineStr"/>
-      <c r="N87" s="27" t="inlineStr">
+      <c r="M87" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N87" s="12" t="n"/>
       <c r="O87" s="12" t="n"/>
-      <c r="P87" s="12" t="n"/>
-      <c r="Q87" s="28" t="n"/>
-      <c r="R87" s="12" t="n"/>
+      <c r="P87" s="28" t="n"/>
+      <c r="Q87" s="12" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
@@ -15054,16 +14708,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M88" s="12" t="inlineStr"/>
-      <c r="N88" s="27" t="inlineStr">
+      <c r="M88" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N88" s="12" t="n"/>
       <c r="O88" s="12" t="n"/>
-      <c r="P88" s="12" t="n"/>
-      <c r="Q88" s="28" t="n"/>
-      <c r="R88" s="12" t="n"/>
+      <c r="P88" s="28" t="n"/>
+      <c r="Q88" s="12" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
@@ -15126,16 +14779,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M89" s="12" t="inlineStr"/>
-      <c r="N89" s="27" t="inlineStr">
+      <c r="M89" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N89" s="12" t="n"/>
       <c r="O89" s="12" t="n"/>
-      <c r="P89" s="12" t="n"/>
-      <c r="Q89" s="28" t="n"/>
-      <c r="R89" s="12" t="n"/>
+      <c r="P89" s="28" t="n"/>
+      <c r="Q89" s="12" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
@@ -15200,16 +14852,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M90" s="12" t="inlineStr"/>
-      <c r="N90" s="27" t="inlineStr">
+      <c r="M90" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N90" s="12" t="n"/>
       <c r="O90" s="12" t="n"/>
-      <c r="P90" s="12" t="n"/>
-      <c r="Q90" s="28" t="n"/>
-      <c r="R90" s="12" t="n"/>
+      <c r="P90" s="28" t="n"/>
+      <c r="Q90" s="12" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
@@ -15272,16 +14923,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M91" s="12" t="inlineStr"/>
-      <c r="N91" s="27" t="inlineStr">
+      <c r="M91" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N91" s="12" t="n"/>
       <c r="O91" s="12" t="n"/>
-      <c r="P91" s="12" t="n"/>
-      <c r="Q91" s="28" t="n"/>
-      <c r="R91" s="12" t="n"/>
+      <c r="P91" s="28" t="n"/>
+      <c r="Q91" s="12" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
@@ -15344,16 +14994,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M92" s="12" t="inlineStr"/>
-      <c r="N92" s="27" t="inlineStr">
+      <c r="M92" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N92" s="12" t="n"/>
       <c r="O92" s="12" t="n"/>
-      <c r="P92" s="12" t="n"/>
-      <c r="Q92" s="28" t="n"/>
-      <c r="R92" s="12" t="n"/>
+      <c r="P92" s="28" t="n"/>
+      <c r="Q92" s="12" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
@@ -15417,16 +15066,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M93" s="12" t="inlineStr"/>
-      <c r="N93" s="27" t="inlineStr">
+      <c r="M93" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N93" s="12" t="n"/>
       <c r="O93" s="12" t="n"/>
-      <c r="P93" s="12" t="n"/>
-      <c r="Q93" s="28" t="n"/>
-      <c r="R93" s="12" t="n"/>
+      <c r="P93" s="28" t="n"/>
+      <c r="Q93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
@@ -15489,16 +15137,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M94" s="12" t="inlineStr"/>
-      <c r="N94" s="27" t="inlineStr">
+      <c r="M94" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N94" s="12" t="n"/>
       <c r="O94" s="12" t="n"/>
-      <c r="P94" s="12" t="n"/>
-      <c r="Q94" s="28" t="n"/>
-      <c r="R94" s="12" t="n"/>
+      <c r="P94" s="28" t="n"/>
+      <c r="Q94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
@@ -15561,16 +15208,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M95" s="12" t="inlineStr"/>
-      <c r="N95" s="27" t="inlineStr">
+      <c r="M95" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N95" s="12" t="n"/>
       <c r="O95" s="12" t="n"/>
-      <c r="P95" s="12" t="n"/>
-      <c r="Q95" s="28" t="n"/>
-      <c r="R95" s="12" t="n"/>
+      <c r="P95" s="28" t="n"/>
+      <c r="Q95" s="12" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
@@ -15633,16 +15279,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M96" s="12" t="inlineStr"/>
-      <c r="N96" s="27" t="inlineStr">
+      <c r="M96" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N96" s="12" t="n"/>
       <c r="O96" s="12" t="n"/>
-      <c r="P96" s="12" t="n"/>
-      <c r="Q96" s="28" t="n"/>
-      <c r="R96" s="12" t="n"/>
+      <c r="P96" s="28" t="n"/>
+      <c r="Q96" s="12" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
@@ -15705,16 +15350,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M97" s="12" t="inlineStr"/>
-      <c r="N97" s="27" t="inlineStr">
+      <c r="M97" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N97" s="12" t="n"/>
       <c r="O97" s="12" t="n"/>
-      <c r="P97" s="12" t="n"/>
-      <c r="Q97" s="28" t="n"/>
-      <c r="R97" s="12" t="n"/>
+      <c r="P97" s="28" t="n"/>
+      <c r="Q97" s="12" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
@@ -15778,16 +15422,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M98" s="12" t="inlineStr"/>
-      <c r="N98" s="27" t="inlineStr">
+      <c r="M98" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N98" s="12" t="n"/>
       <c r="O98" s="12" t="n"/>
-      <c r="P98" s="12" t="n"/>
-      <c r="Q98" s="28" t="n"/>
-      <c r="R98" s="12" t="n"/>
+      <c r="P98" s="28" t="n"/>
+      <c r="Q98" s="12" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
@@ -15850,16 +15493,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M99" s="12" t="inlineStr"/>
-      <c r="N99" s="27" t="inlineStr">
+      <c r="M99" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N99" s="12" t="n"/>
       <c r="O99" s="12" t="n"/>
-      <c r="P99" s="12" t="n"/>
-      <c r="Q99" s="28" t="n"/>
-      <c r="R99" s="12" t="n"/>
+      <c r="P99" s="28" t="n"/>
+      <c r="Q99" s="12" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
@@ -15922,16 +15564,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M100" s="12" t="inlineStr"/>
-      <c r="N100" s="27" t="inlineStr">
+      <c r="M100" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N100" s="12" t="n"/>
       <c r="O100" s="12" t="n"/>
-      <c r="P100" s="12" t="n"/>
-      <c r="Q100" s="28" t="n"/>
-      <c r="R100" s="12" t="n"/>
+      <c r="P100" s="28" t="n"/>
+      <c r="Q100" s="12" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
@@ -15994,16 +15635,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M101" s="12" t="inlineStr"/>
-      <c r="N101" s="27" t="inlineStr">
+      <c r="M101" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N101" s="12" t="n"/>
       <c r="O101" s="12" t="n"/>
-      <c r="P101" s="12" t="n"/>
-      <c r="Q101" s="28" t="n"/>
-      <c r="R101" s="12" t="n"/>
+      <c r="P101" s="28" t="n"/>
+      <c r="Q101" s="12" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
@@ -16067,16 +15707,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M102" s="12" t="inlineStr"/>
-      <c r="N102" s="27" t="inlineStr">
+      <c r="M102" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N102" s="12" t="n"/>
       <c r="O102" s="12" t="n"/>
-      <c r="P102" s="12" t="n"/>
-      <c r="Q102" s="28" t="n"/>
-      <c r="R102" s="12" t="n"/>
+      <c r="P102" s="28" t="n"/>
+      <c r="Q102" s="12" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
@@ -16139,16 +15778,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M103" s="12" t="inlineStr"/>
-      <c r="N103" s="27" t="inlineStr">
+      <c r="M103" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N103" s="12" t="n"/>
       <c r="O103" s="12" t="n"/>
-      <c r="P103" s="12" t="n"/>
-      <c r="Q103" s="28" t="n"/>
-      <c r="R103" s="12" t="n"/>
+      <c r="P103" s="28" t="n"/>
+      <c r="Q103" s="12" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
@@ -16211,16 +15849,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M104" s="12" t="inlineStr"/>
-      <c r="N104" s="27" t="inlineStr">
+      <c r="M104" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N104" s="12" t="n"/>
       <c r="O104" s="12" t="n"/>
-      <c r="P104" s="12" t="n"/>
-      <c r="Q104" s="28" t="n"/>
-      <c r="R104" s="12" t="n"/>
+      <c r="P104" s="28" t="n"/>
+      <c r="Q104" s="12" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
@@ -16284,16 +15921,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M105" s="12" t="inlineStr"/>
-      <c r="N105" s="27" t="inlineStr">
+      <c r="M105" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N105" s="12" t="n"/>
       <c r="O105" s="12" t="n"/>
-      <c r="P105" s="12" t="n"/>
-      <c r="Q105" s="28" t="n"/>
-      <c r="R105" s="12" t="n"/>
+      <c r="P105" s="28" t="n"/>
+      <c r="Q105" s="12" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
@@ -16357,16 +15993,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M106" s="12" t="inlineStr"/>
-      <c r="N106" s="27" t="inlineStr">
+      <c r="M106" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N106" s="12" t="n"/>
       <c r="O106" s="12" t="n"/>
-      <c r="P106" s="12" t="n"/>
-      <c r="Q106" s="28" t="n"/>
-      <c r="R106" s="12" t="n"/>
+      <c r="P106" s="28" t="n"/>
+      <c r="Q106" s="12" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
@@ -16429,16 +16064,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M107" s="12" t="inlineStr"/>
-      <c r="N107" s="27" t="inlineStr">
+      <c r="M107" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N107" s="12" t="n"/>
       <c r="O107" s="12" t="n"/>
-      <c r="P107" s="12" t="n"/>
-      <c r="Q107" s="28" t="n"/>
-      <c r="R107" s="12" t="n"/>
+      <c r="P107" s="28" t="n"/>
+      <c r="Q107" s="12" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
@@ -16501,16 +16135,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M108" s="12" t="inlineStr"/>
-      <c r="N108" s="27" t="inlineStr">
+      <c r="M108" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N108" s="12" t="n"/>
       <c r="O108" s="12" t="n"/>
-      <c r="P108" s="12" t="n"/>
-      <c r="Q108" s="28" t="n"/>
-      <c r="R108" s="12" t="n"/>
+      <c r="P108" s="28" t="n"/>
+      <c r="Q108" s="12" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
@@ -16573,16 +16206,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M109" s="12" t="inlineStr"/>
-      <c r="N109" s="27" t="inlineStr">
+      <c r="M109" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N109" s="12" t="n"/>
       <c r="O109" s="12" t="n"/>
-      <c r="P109" s="12" t="n"/>
-      <c r="Q109" s="28" t="n"/>
-      <c r="R109" s="12" t="n"/>
+      <c r="P109" s="28" t="n"/>
+      <c r="Q109" s="12" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
@@ -16646,16 +16278,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M110" s="12" t="inlineStr"/>
-      <c r="N110" s="27" t="inlineStr">
+      <c r="M110" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N110" s="12" t="n"/>
       <c r="O110" s="12" t="n"/>
-      <c r="P110" s="12" t="n"/>
-      <c r="Q110" s="28" t="n"/>
-      <c r="R110" s="12" t="n"/>
+      <c r="P110" s="28" t="n"/>
+      <c r="Q110" s="12" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
@@ -16718,16 +16349,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M111" s="12" t="inlineStr"/>
-      <c r="N111" s="27" t="inlineStr">
+      <c r="M111" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N111" s="12" t="n"/>
       <c r="O111" s="12" t="n"/>
-      <c r="P111" s="12" t="n"/>
-      <c r="Q111" s="28" t="n"/>
-      <c r="R111" s="12" t="n"/>
+      <c r="P111" s="28" t="n"/>
+      <c r="Q111" s="12" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
@@ -16791,16 +16421,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M112" s="12" t="inlineStr"/>
-      <c r="N112" s="27" t="inlineStr">
+      <c r="M112" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N112" s="12" t="n"/>
       <c r="O112" s="12" t="n"/>
-      <c r="P112" s="12" t="n"/>
-      <c r="Q112" s="28" t="n"/>
-      <c r="R112" s="12" t="n"/>
+      <c r="P112" s="28" t="n"/>
+      <c r="Q112" s="12" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
@@ -16864,16 +16493,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M113" s="12" t="inlineStr"/>
-      <c r="N113" s="27" t="inlineStr">
+      <c r="M113" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N113" s="12" t="n"/>
       <c r="O113" s="12" t="n"/>
-      <c r="P113" s="12" t="n"/>
-      <c r="Q113" s="28" t="n"/>
-      <c r="R113" s="12" t="n"/>
+      <c r="P113" s="28" t="n"/>
+      <c r="Q113" s="12" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
@@ -16936,16 +16564,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M114" s="12" t="inlineStr"/>
-      <c r="N114" s="27" t="inlineStr">
+      <c r="M114" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N114" s="12" t="n"/>
       <c r="O114" s="12" t="n"/>
-      <c r="P114" s="12" t="n"/>
-      <c r="Q114" s="28" t="n"/>
-      <c r="R114" s="12" t="n"/>
+      <c r="P114" s="28" t="n"/>
+      <c r="Q114" s="12" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
@@ -17009,16 +16636,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M115" s="12" t="inlineStr"/>
-      <c r="N115" s="27" t="inlineStr">
+      <c r="M115" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N115" s="12" t="n"/>
       <c r="O115" s="12" t="n"/>
-      <c r="P115" s="12" t="n"/>
-      <c r="Q115" s="28" t="n"/>
-      <c r="R115" s="12" t="n"/>
+      <c r="P115" s="28" t="n"/>
+      <c r="Q115" s="12" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
@@ -17081,16 +16707,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M116" s="12" t="inlineStr"/>
-      <c r="N116" s="27" t="inlineStr">
+      <c r="M116" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N116" s="12" t="n"/>
       <c r="O116" s="12" t="n"/>
-      <c r="P116" s="12" t="n"/>
-      <c r="Q116" s="28" t="n"/>
-      <c r="R116" s="12" t="n"/>
+      <c r="P116" s="28" t="n"/>
+      <c r="Q116" s="12" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
@@ -17153,16 +16778,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M117" s="12" t="inlineStr"/>
-      <c r="N117" s="27" t="inlineStr">
+      <c r="M117" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N117" s="12" t="n"/>
       <c r="O117" s="12" t="n"/>
-      <c r="P117" s="12" t="n"/>
-      <c r="Q117" s="28" t="n"/>
-      <c r="R117" s="12" t="n"/>
+      <c r="P117" s="28" t="n"/>
+      <c r="Q117" s="12" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
@@ -17225,16 +16849,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M118" s="12" t="inlineStr"/>
-      <c r="N118" s="27" t="inlineStr">
+      <c r="M118" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N118" s="12" t="n"/>
       <c r="O118" s="12" t="n"/>
-      <c r="P118" s="12" t="n"/>
-      <c r="Q118" s="28" t="n"/>
-      <c r="R118" s="12" t="n"/>
+      <c r="P118" s="28" t="n"/>
+      <c r="Q118" s="12" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
@@ -17298,16 +16921,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M119" s="12" t="inlineStr"/>
-      <c r="N119" s="27" t="inlineStr">
+      <c r="M119" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N119" s="12" t="n"/>
       <c r="O119" s="12" t="n"/>
-      <c r="P119" s="12" t="n"/>
-      <c r="Q119" s="28" t="n"/>
-      <c r="R119" s="12" t="n"/>
+      <c r="P119" s="28" t="n"/>
+      <c r="Q119" s="12" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
@@ -17372,16 +16994,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M120" s="12" t="inlineStr"/>
-      <c r="N120" s="27" t="inlineStr">
+      <c r="M120" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N120" s="12" t="n"/>
       <c r="O120" s="12" t="n"/>
-      <c r="P120" s="12" t="n"/>
-      <c r="Q120" s="28" t="n"/>
-      <c r="R120" s="12" t="n"/>
+      <c r="P120" s="28" t="n"/>
+      <c r="Q120" s="12" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="12" t="inlineStr">
@@ -17444,16 +17065,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M121" s="12" t="inlineStr"/>
-      <c r="N121" s="27" t="inlineStr">
+      <c r="M121" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N121" s="12" t="n"/>
       <c r="O121" s="12" t="n"/>
-      <c r="P121" s="12" t="n"/>
-      <c r="Q121" s="28" t="n"/>
-      <c r="R121" s="12" t="n"/>
+      <c r="P121" s="28" t="n"/>
+      <c r="Q121" s="12" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
@@ -17516,16 +17136,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M122" s="12" t="inlineStr"/>
-      <c r="N122" s="27" t="inlineStr">
+      <c r="M122" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N122" s="12" t="n"/>
       <c r="O122" s="12" t="n"/>
-      <c r="P122" s="12" t="n"/>
-      <c r="Q122" s="28" t="n"/>
-      <c r="R122" s="12" t="n"/>
+      <c r="P122" s="28" t="n"/>
+      <c r="Q122" s="12" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="12" t="inlineStr">
@@ -17589,16 +17208,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M123" s="12" t="inlineStr"/>
-      <c r="N123" s="27" t="inlineStr">
+      <c r="M123" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N123" s="12" t="n"/>
       <c r="O123" s="12" t="n"/>
-      <c r="P123" s="12" t="n"/>
-      <c r="Q123" s="28" t="n"/>
-      <c r="R123" s="12" t="n"/>
+      <c r="P123" s="28" t="n"/>
+      <c r="Q123" s="12" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
@@ -17661,16 +17279,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M124" s="12" t="inlineStr"/>
-      <c r="N124" s="27" t="inlineStr">
+      <c r="M124" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N124" s="12" t="n"/>
       <c r="O124" s="12" t="n"/>
-      <c r="P124" s="12" t="n"/>
-      <c r="Q124" s="28" t="n"/>
-      <c r="R124" s="12" t="n"/>
+      <c r="P124" s="28" t="n"/>
+      <c r="Q124" s="12" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="12" t="inlineStr">
@@ -17733,16 +17350,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M125" s="12" t="inlineStr"/>
-      <c r="N125" s="27" t="inlineStr">
+      <c r="M125" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N125" s="12" t="n"/>
       <c r="O125" s="12" t="n"/>
-      <c r="P125" s="12" t="n"/>
-      <c r="Q125" s="28" t="n"/>
-      <c r="R125" s="12" t="n"/>
+      <c r="P125" s="28" t="n"/>
+      <c r="Q125" s="12" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="12" t="inlineStr">
@@ -17805,16 +17421,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M126" s="12" t="inlineStr"/>
-      <c r="N126" s="27" t="inlineStr">
+      <c r="M126" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N126" s="12" t="n"/>
       <c r="O126" s="12" t="n"/>
-      <c r="P126" s="12" t="n"/>
-      <c r="Q126" s="28" t="n"/>
-      <c r="R126" s="12" t="n"/>
+      <c r="P126" s="28" t="n"/>
+      <c r="Q126" s="12" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="12" t="inlineStr">
@@ -17878,16 +17493,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M127" s="12" t="inlineStr"/>
-      <c r="N127" s="27" t="inlineStr">
+      <c r="M127" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N127" s="12" t="n"/>
       <c r="O127" s="12" t="n"/>
-      <c r="P127" s="12" t="n"/>
-      <c r="Q127" s="28" t="n"/>
-      <c r="R127" s="12" t="n"/>
+      <c r="P127" s="28" t="n"/>
+      <c r="Q127" s="12" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="inlineStr">
@@ -17950,16 +17564,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M128" s="12" t="inlineStr"/>
-      <c r="N128" s="27" t="inlineStr">
+      <c r="M128" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N128" s="12" t="n"/>
       <c r="O128" s="12" t="n"/>
-      <c r="P128" s="12" t="n"/>
-      <c r="Q128" s="28" t="n"/>
-      <c r="R128" s="12" t="n"/>
+      <c r="P128" s="28" t="n"/>
+      <c r="Q128" s="12" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="12" t="inlineStr">
@@ -18022,16 +17635,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M129" s="12" t="inlineStr"/>
-      <c r="N129" s="27" t="inlineStr">
+      <c r="M129" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N129" s="12" t="n"/>
       <c r="O129" s="12" t="n"/>
-      <c r="P129" s="12" t="n"/>
-      <c r="Q129" s="28" t="n"/>
-      <c r="R129" s="12" t="n"/>
+      <c r="P129" s="28" t="n"/>
+      <c r="Q129" s="12" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="12" t="inlineStr">
@@ -18095,16 +17707,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M130" s="12" t="inlineStr"/>
-      <c r="N130" s="27" t="inlineStr">
+      <c r="M130" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N130" s="12" t="n"/>
       <c r="O130" s="12" t="n"/>
-      <c r="P130" s="12" t="n"/>
-      <c r="Q130" s="28" t="n"/>
-      <c r="R130" s="12" t="n"/>
+      <c r="P130" s="28" t="n"/>
+      <c r="Q130" s="12" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="12" t="inlineStr">
@@ -18169,16 +17780,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M131" s="12" t="inlineStr"/>
-      <c r="N131" s="27" t="inlineStr">
+      <c r="M131" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N131" s="12" t="n"/>
       <c r="O131" s="12" t="n"/>
-      <c r="P131" s="12" t="n"/>
-      <c r="Q131" s="28" t="n"/>
-      <c r="R131" s="12" t="n"/>
+      <c r="P131" s="28" t="n"/>
+      <c r="Q131" s="12" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="inlineStr">
@@ -18241,16 +17851,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M132" s="12" t="inlineStr"/>
-      <c r="N132" s="27" t="inlineStr">
+      <c r="M132" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N132" s="12" t="n"/>
       <c r="O132" s="12" t="n"/>
-      <c r="P132" s="12" t="n"/>
-      <c r="Q132" s="28" t="n"/>
-      <c r="R132" s="12" t="n"/>
+      <c r="P132" s="28" t="n"/>
+      <c r="Q132" s="12" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="12" t="inlineStr">
@@ -18314,16 +17923,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M133" s="12" t="inlineStr"/>
-      <c r="N133" s="27" t="inlineStr">
+      <c r="M133" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N133" s="12" t="n"/>
       <c r="O133" s="12" t="n"/>
-      <c r="P133" s="12" t="n"/>
-      <c r="Q133" s="28" t="n"/>
-      <c r="R133" s="12" t="n"/>
+      <c r="P133" s="28" t="n"/>
+      <c r="Q133" s="12" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="12" t="inlineStr">
@@ -18388,16 +17996,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M134" s="12" t="inlineStr"/>
-      <c r="N134" s="27" t="inlineStr">
+      <c r="M134" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N134" s="12" t="n"/>
       <c r="O134" s="12" t="n"/>
-      <c r="P134" s="12" t="n"/>
-      <c r="Q134" s="28" t="n"/>
-      <c r="R134" s="12" t="n"/>
+      <c r="P134" s="28" t="n"/>
+      <c r="Q134" s="12" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="12" t="inlineStr">
@@ -18460,16 +18067,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M135" s="12" t="inlineStr"/>
-      <c r="N135" s="27" t="inlineStr">
+      <c r="M135" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N135" s="12" t="n"/>
       <c r="O135" s="12" t="n"/>
-      <c r="P135" s="12" t="n"/>
-      <c r="Q135" s="28" t="n"/>
-      <c r="R135" s="12" t="n"/>
+      <c r="P135" s="28" t="n"/>
+      <c r="Q135" s="12" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="12" t="inlineStr">
@@ -18532,16 +18138,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M136" s="12" t="inlineStr"/>
-      <c r="N136" s="27" t="inlineStr">
+      <c r="M136" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N136" s="12" t="n"/>
       <c r="O136" s="12" t="n"/>
-      <c r="P136" s="12" t="n"/>
-      <c r="Q136" s="28" t="n"/>
-      <c r="R136" s="12" t="n"/>
+      <c r="P136" s="28" t="n"/>
+      <c r="Q136" s="12" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="12" t="inlineStr">
@@ -18604,16 +18209,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M137" s="12" t="inlineStr"/>
-      <c r="N137" s="27" t="inlineStr">
+      <c r="M137" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N137" s="12" t="n"/>
       <c r="O137" s="12" t="n"/>
-      <c r="P137" s="12" t="n"/>
-      <c r="Q137" s="28" t="n"/>
-      <c r="R137" s="12" t="n"/>
+      <c r="P137" s="28" t="n"/>
+      <c r="Q137" s="12" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="12" t="inlineStr">
@@ -18676,16 +18280,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M138" s="12" t="inlineStr"/>
-      <c r="N138" s="27" t="inlineStr">
+      <c r="M138" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N138" s="12" t="n"/>
       <c r="O138" s="12" t="n"/>
-      <c r="P138" s="12" t="n"/>
-      <c r="Q138" s="28" t="n"/>
-      <c r="R138" s="12" t="n"/>
+      <c r="P138" s="28" t="n"/>
+      <c r="Q138" s="12" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
@@ -18748,16 +18351,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M139" s="12" t="inlineStr"/>
-      <c r="N139" s="27" t="inlineStr">
+      <c r="M139" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N139" s="12" t="n"/>
       <c r="O139" s="12" t="n"/>
-      <c r="P139" s="12" t="n"/>
-      <c r="Q139" s="28" t="n"/>
-      <c r="R139" s="12" t="n"/>
+      <c r="P139" s="28" t="n"/>
+      <c r="Q139" s="12" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="12" t="inlineStr">
@@ -18820,16 +18422,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M140" s="12" t="inlineStr"/>
-      <c r="N140" s="27" t="inlineStr">
+      <c r="M140" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N140" s="12" t="n"/>
       <c r="O140" s="12" t="n"/>
-      <c r="P140" s="12" t="n"/>
-      <c r="Q140" s="28" t="n"/>
-      <c r="R140" s="12" t="n"/>
+      <c r="P140" s="28" t="n"/>
+      <c r="Q140" s="12" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="12" t="inlineStr">
@@ -18893,16 +18494,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M141" s="12" t="inlineStr"/>
-      <c r="N141" s="27" t="inlineStr">
+      <c r="M141" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N141" s="12" t="n"/>
       <c r="O141" s="12" t="n"/>
-      <c r="P141" s="12" t="n"/>
-      <c r="Q141" s="28" t="n"/>
-      <c r="R141" s="12" t="n"/>
+      <c r="P141" s="28" t="n"/>
+      <c r="Q141" s="12" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="12" t="inlineStr">
@@ -18965,16 +18565,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M142" s="12" t="inlineStr"/>
-      <c r="N142" s="27" t="inlineStr">
+      <c r="M142" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N142" s="12" t="n"/>
       <c r="O142" s="12" t="n"/>
-      <c r="P142" s="12" t="n"/>
-      <c r="Q142" s="28" t="n"/>
-      <c r="R142" s="12" t="n"/>
+      <c r="P142" s="28" t="n"/>
+      <c r="Q142" s="12" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="12" t="inlineStr">
@@ -19037,16 +18636,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M143" s="12" t="inlineStr"/>
-      <c r="N143" s="27" t="inlineStr">
+      <c r="M143" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N143" s="12" t="n"/>
       <c r="O143" s="12" t="n"/>
-      <c r="P143" s="12" t="n"/>
-      <c r="Q143" s="28" t="n"/>
-      <c r="R143" s="12" t="n"/>
+      <c r="P143" s="28" t="n"/>
+      <c r="Q143" s="12" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="12" t="inlineStr">
@@ -19110,16 +18708,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M144" s="12" t="inlineStr"/>
-      <c r="N144" s="27" t="inlineStr">
+      <c r="M144" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N144" s="12" t="n"/>
       <c r="O144" s="12" t="n"/>
-      <c r="P144" s="12" t="n"/>
-      <c r="Q144" s="28" t="n"/>
-      <c r="R144" s="12" t="n"/>
+      <c r="P144" s="28" t="n"/>
+      <c r="Q144" s="12" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="12" t="inlineStr">
@@ -19182,16 +18779,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M145" s="12" t="inlineStr"/>
-      <c r="N145" s="27" t="inlineStr">
+      <c r="M145" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N145" s="12" t="n"/>
       <c r="O145" s="12" t="n"/>
-      <c r="P145" s="12" t="n"/>
-      <c r="Q145" s="28" t="n"/>
-      <c r="R145" s="12" t="n"/>
+      <c r="P145" s="28" t="n"/>
+      <c r="Q145" s="12" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="12" t="inlineStr">
@@ -19254,16 +18850,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M146" s="12" t="inlineStr"/>
-      <c r="N146" s="27" t="inlineStr">
+      <c r="M146" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N146" s="12" t="n"/>
       <c r="O146" s="12" t="n"/>
-      <c r="P146" s="12" t="n"/>
-      <c r="Q146" s="28" t="n"/>
-      <c r="R146" s="12" t="n"/>
+      <c r="P146" s="28" t="n"/>
+      <c r="Q146" s="12" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="12" t="inlineStr">
@@ -19326,16 +18921,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M147" s="12" t="inlineStr"/>
-      <c r="N147" s="27" t="inlineStr">
+      <c r="M147" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N147" s="12" t="n"/>
       <c r="O147" s="12" t="n"/>
-      <c r="P147" s="12" t="n"/>
-      <c r="Q147" s="28" t="n"/>
-      <c r="R147" s="12" t="n"/>
+      <c r="P147" s="28" t="n"/>
+      <c r="Q147" s="12" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="12" t="inlineStr">
@@ -19399,16 +18993,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M148" s="12" t="inlineStr"/>
-      <c r="N148" s="27" t="inlineStr">
+      <c r="M148" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N148" s="12" t="n"/>
       <c r="O148" s="12" t="n"/>
-      <c r="P148" s="12" t="n"/>
-      <c r="Q148" s="28" t="n"/>
-      <c r="R148" s="12" t="n"/>
+      <c r="P148" s="28" t="n"/>
+      <c r="Q148" s="12" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="12" t="inlineStr">
@@ -19471,16 +19064,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M149" s="12" t="inlineStr"/>
-      <c r="N149" s="27" t="inlineStr">
+      <c r="M149" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N149" s="12" t="n"/>
       <c r="O149" s="12" t="n"/>
-      <c r="P149" s="12" t="n"/>
-      <c r="Q149" s="28" t="n"/>
-      <c r="R149" s="12" t="n"/>
+      <c r="P149" s="28" t="n"/>
+      <c r="Q149" s="12" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="12" t="inlineStr">
@@ -19535,7 +19127,7 @@
       </c>
       <c r="K150" s="12" t="inlineStr">
         <is>
-          <t>Not in the report list; the call returns HTTP 403.</t>
+          <t>Not in the report list; the request is refused.</t>
         </is>
       </c>
       <c r="L150" s="12" t="inlineStr">
@@ -19543,16 +19135,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M150" s="12" t="inlineStr"/>
-      <c r="N150" s="27" t="inlineStr">
+      <c r="M150" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N150" s="12" t="n"/>
       <c r="O150" s="12" t="n"/>
-      <c r="P150" s="12" t="n"/>
-      <c r="Q150" s="28" t="n"/>
-      <c r="R150" s="12" t="n"/>
+      <c r="P150" s="28" t="n"/>
+      <c r="Q150" s="12" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="12" t="inlineStr">
@@ -19615,16 +19206,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M151" s="12" t="inlineStr"/>
-      <c r="N151" s="27" t="inlineStr">
+      <c r="M151" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N151" s="12" t="n"/>
       <c r="O151" s="12" t="n"/>
-      <c r="P151" s="12" t="n"/>
-      <c r="Q151" s="28" t="n"/>
-      <c r="R151" s="12" t="n"/>
+      <c r="P151" s="28" t="n"/>
+      <c r="Q151" s="12" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="12" t="inlineStr">
@@ -19688,16 +19278,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M152" s="12" t="inlineStr"/>
-      <c r="N152" s="27" t="inlineStr">
+      <c r="M152" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N152" s="12" t="n"/>
       <c r="O152" s="12" t="n"/>
-      <c r="P152" s="12" t="n"/>
-      <c r="Q152" s="28" t="n"/>
-      <c r="R152" s="12" t="n"/>
+      <c r="P152" s="28" t="n"/>
+      <c r="Q152" s="12" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="12" t="inlineStr">
@@ -19761,16 +19350,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M153" s="12" t="inlineStr"/>
-      <c r="N153" s="27" t="inlineStr">
+      <c r="M153" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N153" s="12" t="n"/>
       <c r="O153" s="12" t="n"/>
-      <c r="P153" s="12" t="n"/>
-      <c r="Q153" s="28" t="n"/>
-      <c r="R153" s="12" t="n"/>
+      <c r="P153" s="28" t="n"/>
+      <c r="Q153" s="12" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="12" t="inlineStr">
@@ -19833,16 +19421,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M154" s="12" t="inlineStr"/>
-      <c r="N154" s="27" t="inlineStr">
+      <c r="M154" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N154" s="12" t="n"/>
       <c r="O154" s="12" t="n"/>
-      <c r="P154" s="12" t="n"/>
-      <c r="Q154" s="28" t="n"/>
-      <c r="R154" s="12" t="n"/>
+      <c r="P154" s="28" t="n"/>
+      <c r="Q154" s="12" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="12" t="inlineStr">
@@ -19882,7 +19469,7 @@
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I155" s="12" t="inlineStr">
@@ -19892,12 +19479,12 @@
       </c>
       <c r="J155" s="12" t="inlineStr">
         <is>
-          <t>1. Try to update and delete a log entry through the API as an administrator.</t>
+          <t>1. Try to update and delete a log entry by a direct request as an administrator.</t>
         </is>
       </c>
       <c r="K155" s="12" t="inlineStr">
         <is>
-          <t>No edit or delete action exists; both calls are refused.</t>
+          <t>No edit or delete action exists; both requests are refused.</t>
         </is>
       </c>
       <c r="L155" s="12" t="inlineStr">
@@ -19905,16 +19492,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M155" s="12" t="inlineStr"/>
-      <c r="N155" s="27" t="inlineStr">
+      <c r="M155" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N155" s="12" t="n"/>
       <c r="O155" s="12" t="n"/>
-      <c r="P155" s="12" t="n"/>
-      <c r="Q155" s="28" t="n"/>
-      <c r="R155" s="12" t="n"/>
+      <c r="P155" s="28" t="n"/>
+      <c r="Q155" s="12" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="12" t="inlineStr">
@@ -19978,16 +19564,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M156" s="12" t="inlineStr"/>
-      <c r="N156" s="27" t="inlineStr">
+      <c r="M156" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N156" s="12" t="n"/>
       <c r="O156" s="12" t="n"/>
-      <c r="P156" s="12" t="n"/>
-      <c r="Q156" s="28" t="n"/>
-      <c r="R156" s="12" t="n"/>
+      <c r="P156" s="28" t="n"/>
+      <c r="Q156" s="12" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="12" t="inlineStr">
@@ -20050,16 +19635,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M157" s="12" t="inlineStr"/>
-      <c r="N157" s="27" t="inlineStr">
+      <c r="M157" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N157" s="12" t="n"/>
       <c r="O157" s="12" t="n"/>
-      <c r="P157" s="12" t="n"/>
-      <c r="Q157" s="28" t="n"/>
-      <c r="R157" s="12" t="n"/>
+      <c r="P157" s="28" t="n"/>
+      <c r="Q157" s="12" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="12" t="inlineStr">
@@ -20122,16 +19706,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M158" s="12" t="inlineStr"/>
-      <c r="N158" s="27" t="inlineStr">
+      <c r="M158" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N158" s="12" t="n"/>
       <c r="O158" s="12" t="n"/>
-      <c r="P158" s="12" t="n"/>
-      <c r="Q158" s="28" t="n"/>
-      <c r="R158" s="12" t="n"/>
+      <c r="P158" s="28" t="n"/>
+      <c r="Q158" s="12" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="12" t="inlineStr">
@@ -20195,16 +19778,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M159" s="12" t="inlineStr"/>
-      <c r="N159" s="27" t="inlineStr">
+      <c r="M159" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N159" s="12" t="n"/>
       <c r="O159" s="12" t="n"/>
-      <c r="P159" s="12" t="n"/>
-      <c r="Q159" s="28" t="n"/>
-      <c r="R159" s="12" t="n"/>
+      <c r="P159" s="28" t="n"/>
+      <c r="Q159" s="12" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="12" t="inlineStr">
@@ -20269,16 +19851,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M160" s="12" t="inlineStr"/>
-      <c r="N160" s="27" t="inlineStr">
+      <c r="M160" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N160" s="12" t="n"/>
       <c r="O160" s="12" t="n"/>
-      <c r="P160" s="12" t="n"/>
-      <c r="Q160" s="28" t="n"/>
-      <c r="R160" s="12" t="n"/>
+      <c r="P160" s="28" t="n"/>
+      <c r="Q160" s="12" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="12" t="inlineStr">
@@ -20343,16 +19924,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M161" s="12" t="inlineStr"/>
-      <c r="N161" s="27" t="inlineStr">
+      <c r="M161" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N161" s="12" t="n"/>
       <c r="O161" s="12" t="n"/>
-      <c r="P161" s="12" t="n"/>
-      <c r="Q161" s="28" t="n"/>
-      <c r="R161" s="12" t="n"/>
+      <c r="P161" s="28" t="n"/>
+      <c r="Q161" s="12" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="12" t="inlineStr">
@@ -20415,16 +19995,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M162" s="12" t="inlineStr"/>
-      <c r="N162" s="27" t="inlineStr">
+      <c r="M162" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N162" s="12" t="n"/>
       <c r="O162" s="12" t="n"/>
-      <c r="P162" s="12" t="n"/>
-      <c r="Q162" s="28" t="n"/>
-      <c r="R162" s="12" t="n"/>
+      <c r="P162" s="28" t="n"/>
+      <c r="Q162" s="12" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="12" t="inlineStr">
@@ -20487,16 +20066,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M163" s="12" t="inlineStr"/>
-      <c r="N163" s="27" t="inlineStr">
+      <c r="M163" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N163" s="12" t="n"/>
       <c r="O163" s="12" t="n"/>
-      <c r="P163" s="12" t="n"/>
-      <c r="Q163" s="28" t="n"/>
-      <c r="R163" s="12" t="n"/>
+      <c r="P163" s="28" t="n"/>
+      <c r="Q163" s="12" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="12" t="inlineStr">
@@ -20561,16 +20139,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M164" s="12" t="inlineStr"/>
-      <c r="N164" s="27" t="inlineStr">
+      <c r="M164" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N164" s="12" t="n"/>
       <c r="O164" s="12" t="n"/>
-      <c r="P164" s="12" t="n"/>
-      <c r="Q164" s="28" t="n"/>
-      <c r="R164" s="12" t="n"/>
+      <c r="P164" s="28" t="n"/>
+      <c r="Q164" s="12" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="12" t="inlineStr">
@@ -20633,16 +20210,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M165" s="12" t="inlineStr"/>
-      <c r="N165" s="27" t="inlineStr">
+      <c r="M165" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N165" s="12" t="n"/>
       <c r="O165" s="12" t="n"/>
-      <c r="P165" s="12" t="n"/>
-      <c r="Q165" s="28" t="n"/>
-      <c r="R165" s="12" t="n"/>
+      <c r="P165" s="28" t="n"/>
+      <c r="Q165" s="12" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="12" t="inlineStr">
@@ -20705,16 +20281,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M166" s="12" t="inlineStr"/>
-      <c r="N166" s="27" t="inlineStr">
+      <c r="M166" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N166" s="12" t="n"/>
       <c r="O166" s="12" t="n"/>
-      <c r="P166" s="12" t="n"/>
-      <c r="Q166" s="28" t="n"/>
-      <c r="R166" s="12" t="n"/>
+      <c r="P166" s="28" t="n"/>
+      <c r="Q166" s="12" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="12" t="inlineStr">
@@ -20777,16 +20352,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M167" s="12" t="inlineStr"/>
-      <c r="N167" s="27" t="inlineStr">
+      <c r="M167" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N167" s="12" t="n"/>
       <c r="O167" s="12" t="n"/>
-      <c r="P167" s="12" t="n"/>
-      <c r="Q167" s="28" t="n"/>
-      <c r="R167" s="12" t="n"/>
+      <c r="P167" s="28" t="n"/>
+      <c r="Q167" s="12" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="12" t="inlineStr">
@@ -20850,16 +20424,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M168" s="12" t="inlineStr"/>
-      <c r="N168" s="27" t="inlineStr">
+      <c r="M168" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N168" s="12" t="n"/>
       <c r="O168" s="12" t="n"/>
-      <c r="P168" s="12" t="n"/>
-      <c r="Q168" s="28" t="n"/>
-      <c r="R168" s="12" t="n"/>
+      <c r="P168" s="28" t="n"/>
+      <c r="Q168" s="12" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="12" t="inlineStr">
@@ -20923,16 +20496,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M169" s="12" t="inlineStr"/>
-      <c r="N169" s="27" t="inlineStr">
+      <c r="M169" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N169" s="12" t="n"/>
       <c r="O169" s="12" t="n"/>
-      <c r="P169" s="12" t="n"/>
-      <c r="Q169" s="28" t="n"/>
-      <c r="R169" s="12" t="n"/>
+      <c r="P169" s="28" t="n"/>
+      <c r="Q169" s="12" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="12" t="inlineStr">
@@ -20996,16 +20568,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M170" s="12" t="inlineStr"/>
-      <c r="N170" s="27" t="inlineStr">
+      <c r="M170" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N170" s="12" t="n"/>
       <c r="O170" s="12" t="n"/>
-      <c r="P170" s="12" t="n"/>
-      <c r="Q170" s="28" t="n"/>
-      <c r="R170" s="12" t="n"/>
+      <c r="P170" s="28" t="n"/>
+      <c r="Q170" s="12" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="12" t="inlineStr">
@@ -21068,16 +20639,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M171" s="12" t="inlineStr"/>
-      <c r="N171" s="27" t="inlineStr">
+      <c r="M171" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N171" s="12" t="n"/>
       <c r="O171" s="12" t="n"/>
-      <c r="P171" s="12" t="n"/>
-      <c r="Q171" s="28" t="n"/>
-      <c r="R171" s="12" t="n"/>
+      <c r="P171" s="28" t="n"/>
+      <c r="Q171" s="12" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="12" t="inlineStr">
@@ -21142,16 +20712,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M172" s="12" t="inlineStr"/>
-      <c r="N172" s="27" t="inlineStr">
+      <c r="M172" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N172" s="12" t="n"/>
       <c r="O172" s="12" t="n"/>
-      <c r="P172" s="12" t="n"/>
-      <c r="Q172" s="28" t="n"/>
-      <c r="R172" s="12" t="n"/>
+      <c r="P172" s="28" t="n"/>
+      <c r="Q172" s="12" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="12" t="inlineStr">
@@ -21214,16 +20783,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M173" s="12" t="inlineStr"/>
-      <c r="N173" s="27" t="inlineStr">
+      <c r="M173" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N173" s="12" t="n"/>
       <c r="O173" s="12" t="n"/>
-      <c r="P173" s="12" t="n"/>
-      <c r="Q173" s="28" t="n"/>
-      <c r="R173" s="12" t="n"/>
+      <c r="P173" s="28" t="n"/>
+      <c r="Q173" s="12" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="12" t="inlineStr">
@@ -21286,16 +20854,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M174" s="12" t="inlineStr"/>
-      <c r="N174" s="27" t="inlineStr">
+      <c r="M174" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N174" s="12" t="n"/>
       <c r="O174" s="12" t="n"/>
-      <c r="P174" s="12" t="n"/>
-      <c r="Q174" s="28" t="n"/>
-      <c r="R174" s="12" t="n"/>
+      <c r="P174" s="28" t="n"/>
+      <c r="Q174" s="12" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="12" t="inlineStr">
@@ -21358,16 +20925,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M175" s="12" t="inlineStr"/>
-      <c r="N175" s="27" t="inlineStr">
+      <c r="M175" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N175" s="12" t="n"/>
       <c r="O175" s="12" t="n"/>
-      <c r="P175" s="12" t="n"/>
-      <c r="Q175" s="28" t="n"/>
-      <c r="R175" s="12" t="n"/>
+      <c r="P175" s="28" t="n"/>
+      <c r="Q175" s="12" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="12" t="inlineStr">
@@ -21430,16 +20996,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M176" s="12" t="inlineStr"/>
-      <c r="N176" s="27" t="inlineStr">
+      <c r="M176" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N176" s="12" t="n"/>
       <c r="O176" s="12" t="n"/>
-      <c r="P176" s="12" t="n"/>
-      <c r="Q176" s="28" t="n"/>
-      <c r="R176" s="12" t="n"/>
+      <c r="P176" s="28" t="n"/>
+      <c r="Q176" s="12" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="12" t="inlineStr">
@@ -21502,16 +21067,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M177" s="12" t="inlineStr"/>
-      <c r="N177" s="27" t="inlineStr">
+      <c r="M177" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N177" s="12" t="n"/>
       <c r="O177" s="12" t="n"/>
-      <c r="P177" s="12" t="n"/>
-      <c r="Q177" s="28" t="n"/>
-      <c r="R177" s="12" t="n"/>
+      <c r="P177" s="28" t="n"/>
+      <c r="Q177" s="12" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="12" t="inlineStr">
@@ -21576,16 +21140,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M178" s="12" t="inlineStr"/>
-      <c r="N178" s="27" t="inlineStr">
+      <c r="M178" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N178" s="12" t="n"/>
       <c r="O178" s="12" t="n"/>
-      <c r="P178" s="12" t="n"/>
-      <c r="Q178" s="28" t="n"/>
-      <c r="R178" s="12" t="n"/>
+      <c r="P178" s="28" t="n"/>
+      <c r="Q178" s="12" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="12" t="inlineStr">
@@ -21648,16 +21211,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M179" s="12" t="inlineStr"/>
-      <c r="N179" s="27" t="inlineStr">
+      <c r="M179" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N179" s="12" t="n"/>
       <c r="O179" s="12" t="n"/>
-      <c r="P179" s="12" t="n"/>
-      <c r="Q179" s="28" t="n"/>
-      <c r="R179" s="12" t="n"/>
+      <c r="P179" s="28" t="n"/>
+      <c r="Q179" s="12" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="12" t="inlineStr">
@@ -21721,16 +21283,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M180" s="12" t="inlineStr"/>
-      <c r="N180" s="27" t="inlineStr">
+      <c r="M180" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N180" s="12" t="n"/>
       <c r="O180" s="12" t="n"/>
-      <c r="P180" s="12" t="n"/>
-      <c r="Q180" s="28" t="n"/>
-      <c r="R180" s="12" t="n"/>
+      <c r="P180" s="28" t="n"/>
+      <c r="Q180" s="12" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="12" t="inlineStr">
@@ -21795,16 +21356,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M181" s="12" t="inlineStr"/>
-      <c r="N181" s="27" t="inlineStr">
+      <c r="M181" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N181" s="12" t="n"/>
       <c r="O181" s="12" t="n"/>
-      <c r="P181" s="12" t="n"/>
-      <c r="Q181" s="28" t="n"/>
-      <c r="R181" s="12" t="n"/>
+      <c r="P181" s="28" t="n"/>
+      <c r="Q181" s="12" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="12" t="inlineStr">
@@ -21867,16 +21427,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M182" s="12" t="inlineStr"/>
-      <c r="N182" s="27" t="inlineStr">
+      <c r="M182" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N182" s="12" t="n"/>
       <c r="O182" s="12" t="n"/>
-      <c r="P182" s="12" t="n"/>
-      <c r="Q182" s="28" t="n"/>
-      <c r="R182" s="12" t="n"/>
+      <c r="P182" s="28" t="n"/>
+      <c r="Q182" s="12" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="12" t="inlineStr">
@@ -21941,16 +21500,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M183" s="12" t="inlineStr"/>
-      <c r="N183" s="27" t="inlineStr">
+      <c r="M183" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N183" s="12" t="n"/>
       <c r="O183" s="12" t="n"/>
-      <c r="P183" s="12" t="n"/>
-      <c r="Q183" s="28" t="n"/>
-      <c r="R183" s="12" t="n"/>
+      <c r="P183" s="28" t="n"/>
+      <c r="Q183" s="12" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="12" t="inlineStr">
@@ -22014,16 +21572,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M184" s="12" t="inlineStr"/>
-      <c r="N184" s="27" t="inlineStr">
+      <c r="M184" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N184" s="12" t="n"/>
       <c r="O184" s="12" t="n"/>
-      <c r="P184" s="12" t="n"/>
-      <c r="Q184" s="28" t="n"/>
-      <c r="R184" s="12" t="n"/>
+      <c r="P184" s="28" t="n"/>
+      <c r="Q184" s="12" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="12" t="inlineStr">
@@ -22087,23 +21644,22 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M185" s="12" t="inlineStr"/>
-      <c r="N185" s="27" t="inlineStr">
+      <c r="M185" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N185" s="12" t="n"/>
       <c r="O185" s="12" t="n"/>
-      <c r="P185" s="12" t="n"/>
-      <c r="Q185" s="28" t="n"/>
-      <c r="R185" s="12" t="n"/>
+      <c r="P185" s="28" t="n"/>
+      <c r="Q185" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R185"/>
+  <autoFilter ref="A4:Q185"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A2:Q2"/>
   </mergeCells>
-  <conditionalFormatting sqref="N5:N685">
+  <conditionalFormatting sqref="M5:M685">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -22117,19 +21673,19 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:R685">
+  <conditionalFormatting sqref="A5:Q685">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="F5:F685" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Choose a value from the list (Type)." type="list">
-      <formula1>'_lists'!$B$1:$B$7</formula1>
+      <formula1>'_lists'!$B$1:$B$9</formula1>
     </dataValidation>
     <dataValidation sqref="L5:L685" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'_lists'!$C$1:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N685" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="M5:M685" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$D$1:$D$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -22153,7 +21709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22165,7 +21721,6 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -22192,7 +21747,6 @@
       <c r="G3" s="25" t="n"/>
       <c r="H3" s="25" t="n"/>
       <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -22237,11 +21791,6 @@
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="J4" s="26" t="inlineStr">
-        <is>
           <t>Coverage</t>
         </is>
       </c>
@@ -22279,10 +21828,7 @@
       <c r="H5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22321,10 +21867,7 @@
       <c r="H6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22363,10 +21906,7 @@
       <c r="H7" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22405,10 +21945,7 @@
       <c r="H8" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22447,10 +21984,7 @@
       <c r="H9" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27" t="inlineStr">
+      <c r="I9" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22489,10 +22023,7 @@
       <c r="H10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="27" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22531,10 +22062,7 @@
       <c r="H11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="27" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22573,10 +22101,7 @@
       <c r="H12" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="27" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22615,10 +22140,7 @@
       <c r="H13" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="27" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22657,10 +22179,7 @@
       <c r="H14" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="27" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22699,10 +22218,7 @@
       <c r="H15" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="27" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22741,10 +22257,7 @@
       <c r="H16" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="27" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22783,10 +22296,7 @@
       <c r="H17" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="27" t="inlineStr">
+      <c r="I17" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22825,10 +22335,7 @@
       <c r="H18" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="27" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22867,10 +22374,7 @@
       <c r="H19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="27" t="inlineStr">
+      <c r="I19" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22909,10 +22413,7 @@
       <c r="H20" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="27" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22951,10 +22452,7 @@
       <c r="H21" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="27" t="inlineStr">
+      <c r="I21" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -22993,10 +22491,7 @@
       <c r="H22" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="27" t="inlineStr">
+      <c r="I22" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23035,10 +22530,7 @@
       <c r="H23" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="27" t="inlineStr">
+      <c r="I23" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23077,10 +22569,7 @@
       <c r="H24" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="27" t="inlineStr">
+      <c r="I24" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23119,10 +22608,7 @@
       <c r="H25" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="27" t="inlineStr">
+      <c r="I25" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23161,10 +22647,7 @@
       <c r="H26" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="27" t="inlineStr">
+      <c r="I26" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23203,10 +22686,7 @@
       <c r="H27" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="27" t="inlineStr">
+      <c r="I27" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23245,10 +22725,7 @@
       <c r="H28" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="27" t="inlineStr">
+      <c r="I28" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23287,10 +22764,7 @@
       <c r="H29" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="27" t="inlineStr">
+      <c r="I29" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23329,10 +22803,7 @@
       <c r="H30" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="27" t="inlineStr">
+      <c r="I30" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23371,10 +22842,7 @@
       <c r="H31" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="27" t="inlineStr">
+      <c r="I31" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23413,10 +22881,7 @@
       <c r="H32" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="27" t="inlineStr">
+      <c r="I32" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23455,10 +22920,7 @@
       <c r="H33" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="27" t="inlineStr">
+      <c r="I33" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23497,10 +22959,7 @@
       <c r="H34" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="27" t="inlineStr">
+      <c r="I34" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23539,10 +22998,7 @@
       <c r="H35" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="27" t="inlineStr">
+      <c r="I35" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23581,10 +23037,7 @@
       <c r="H36" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="27" t="inlineStr">
+      <c r="I36" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23623,10 +23076,7 @@
       <c r="H37" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="27" t="inlineStr">
+      <c r="I37" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23665,10 +23115,7 @@
       <c r="H38" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="27" t="inlineStr">
+      <c r="I38" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23707,10 +23154,7 @@
       <c r="H39" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="27" t="inlineStr">
+      <c r="I39" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23749,10 +23193,7 @@
       <c r="H40" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="27" t="inlineStr">
+      <c r="I40" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23791,10 +23232,7 @@
       <c r="H41" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="27" t="inlineStr">
+      <c r="I41" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23833,10 +23271,7 @@
       <c r="H42" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="27" t="inlineStr">
+      <c r="I42" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23875,10 +23310,7 @@
       <c r="H43" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="27" t="inlineStr">
+      <c r="I43" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23917,10 +23349,7 @@
       <c r="H44" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="27" t="inlineStr">
+      <c r="I44" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -23959,10 +23388,7 @@
       <c r="H45" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="27" t="inlineStr">
+      <c r="I45" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24001,10 +23427,7 @@
       <c r="H46" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="27" t="inlineStr">
+      <c r="I46" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24043,10 +23466,7 @@
       <c r="H47" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="27" t="inlineStr">
+      <c r="I47" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24085,10 +23505,7 @@
       <c r="H48" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="27" t="inlineStr">
+      <c r="I48" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24123,10 +23540,7 @@
       <c r="H49" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="27" t="inlineStr">
+      <c r="I49" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24161,10 +23575,7 @@
       <c r="H50" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="I50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="27" t="inlineStr">
+      <c r="I50" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24199,10 +23610,7 @@
       <c r="H51" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="27" t="inlineStr">
+      <c r="I51" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24237,10 +23645,7 @@
       <c r="H52" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="27" t="inlineStr">
+      <c r="I52" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24275,10 +23680,7 @@
       <c r="H53" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="I53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="27" t="inlineStr">
+      <c r="I53" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24313,10 +23715,7 @@
       <c r="H54" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="27" t="inlineStr">
+      <c r="I54" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24351,10 +23750,7 @@
       <c r="H55" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="27" t="inlineStr">
+      <c r="I55" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24389,10 +23785,7 @@
       <c r="H56" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="I56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="27" t="inlineStr">
+      <c r="I56" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24427,10 +23820,7 @@
       <c r="H57" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="27" t="inlineStr">
+      <c r="I57" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24465,10 +23855,7 @@
       <c r="H58" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="27" t="inlineStr">
+      <c r="I58" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24503,10 +23890,7 @@
       <c r="H59" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="27" t="inlineStr">
+      <c r="I59" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24541,10 +23925,7 @@
       <c r="H60" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="27" t="inlineStr">
+      <c r="I60" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24579,10 +23960,7 @@
       <c r="H61" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="27" t="inlineStr">
+      <c r="I61" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24617,10 +23995,7 @@
       <c r="H62" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I62" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="27" t="inlineStr">
+      <c r="I62" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24655,10 +24030,7 @@
       <c r="H63" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="27" t="inlineStr">
+      <c r="I63" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24693,10 +24065,7 @@
       <c r="H64" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I64" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="27" t="inlineStr">
+      <c r="I64" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24731,10 +24100,7 @@
       <c r="H65" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="27" t="inlineStr">
+      <c r="I65" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24769,10 +24135,7 @@
       <c r="H66" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I66" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="27" t="inlineStr">
+      <c r="I66" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24807,10 +24170,7 @@
       <c r="H67" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="27" t="inlineStr">
+      <c r="I67" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24845,10 +24205,7 @@
       <c r="H68" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I68" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="27" t="inlineStr">
+      <c r="I68" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24883,10 +24240,7 @@
       <c r="H69" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="27" t="inlineStr">
+      <c r="I69" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24921,10 +24275,7 @@
       <c r="H70" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="27" t="inlineStr">
+      <c r="I70" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -24959,32 +24310,29 @@
       <c r="H71" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="27" t="inlineStr">
+      <c r="I71" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J71"/>
+  <autoFilter ref="A4:I71"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5:J571">
+  <conditionalFormatting sqref="I5:I571">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"GAP"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:J571">
+  <conditionalFormatting sqref="A5:I571">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J571" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coverage" error="Choose a value from the list (Coverage)." type="list">
+    <dataValidation sqref="I5:I571" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coverage" error="Choose a value from the list (Coverage)." type="list">
       <formula1>'_lists'!$E$1:$E$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -25079,12 +24427,12 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>miglead (DATA_MIGRATION_LEAD), migsteward (DATA_STEWARD), migowner and migowner2 (DATA_OWNER), migops (MIGRATION_OPERATOR), migrecon (MIGRATION_RECON_APPROVER), miggonogo (MIGRATION_GONOGO), legacyaudit (LEGACY_INQUIRY), legacyrev (LEGACY_ACCESS_REVIEWER), topmgmt (TOP_MANAGEMENT_APPROVER), plus the built Operations users (cashier, cashiertl, commrectl, remit, adjuster, adjtl, reconhandler, ao).</t>
+          <t>miglead (DATA_MIGRATION_LEAD), migsteward (DATA_STEWARD), migowner and migowner2 (DATA_OWNER), migops (MIGRATION_OPERATOR), migrecon (MIGRATION_RECON_APPROVER), miggonogo (MIGRATION_GONOGO), legacyaudit (LEGACY_INQUIRY), legacyrev (LEGACY_ACCESS_REVIEWER), topmgmt (TOP_MANAGEMENT_APPROVER), plus the Operations users (cashier, cashiertl, commrectl, remit, adjuster, adjtl, reconhandler, ao).</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Planned seed data V1980 of the build design; existing Operations SIT/UAT users</t>
+          <t>Seed data; existing Operations SIT/UAT users</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -25109,7 +24457,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Masked test extracts in backend/src/main/resources/db/seed/migration/ (build wave DM3) prepared by the test lead in the workbook layouts</t>
+          <t>Masked test extracts prepared by the test lead in the workbook layouts</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
@@ -25304,12 +24652,12 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Parameters as delivered - MIG_ENVIRONMENT_CLASS NON_PRODUCTION, MIG_STAGING_RETENTION_DAYS 5, MIG_CHUNK_SIZE 500, MIG_PARTITIONS 4, MIG_AMOUNT_TOLERANCE 0.00, MIG_MAX_ERROR_RATE_MASTER 0.5, MIG_MAX_ERROR_RATE_FINANCIAL 0, MIG_CLIENT_MATCH_AUTO 90, MIG_CLIENT_MATCH_REVIEW 60, MIG_ARCHIVE_EXPORT_MAX_ROWS 1000, MIG_ACCESS_EXPORT_ALERT_ROWS 5000, MIG_OPENING_VALUE_DATE 1 January 2028, MIG_GOLIVE_RENEWAL_TO 31 May 2028, MIG_RENEWAL_URGENT_TO 31 January 2028, MIG_RESUBMIT_DEADLINE T-1 12:00; legacy control accounts, Migration Clearing and LG_ rule lines set up on the test chart.</t>
+          <t>Parameters as configured - MIG_ENVIRONMENT_CLASS NON_PRODUCTION, MIG_STAGING_RETENTION_DAYS 5, MIG_CHUNK_SIZE 500, MIG_PARTITIONS 4, MIG_AMOUNT_TOLERANCE 0.00, MIG_MAX_ERROR_RATE_MASTER 0.5, MIG_MAX_ERROR_RATE_FINANCIAL 0, MIG_CLIENT_MATCH_AUTO 90, MIG_CLIENT_MATCH_REVIEW 60, MIG_ARCHIVE_EXPORT_MAX_ROWS 1000, MIG_ACCESS_EXPORT_ALERT_ROWS 5000, MIG_OPENING_VALUE_DATE 1 January 2028, MIG_GOLIVE_RENEWAL_TO 31 May 2028, MIG_RENEWAL_URGENT_TO 31 January 2028, MIG_RESUBMIT_DEADLINE T-1 12:00; legacy control accounts, Migration Clearing and LG_ rule lines set up on the test chart.</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Configuration delivered with the build (FRS section 9); seed data V1982</t>
+          <t>Configuration of the SIT environment (FRS section 9); seed data</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
@@ -25334,7 +24682,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Built Operations seed data; payment file prepared by the test lead</t>
+          <t>Operations seed data; payment file prepared by the test lead</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
@@ -25371,7 +24719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -25381,12 +24729,11 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -25416,7 +24763,6 @@
       <c r="J3" s="25" t="n"/>
       <c r="K3" s="25" t="n"/>
       <c r="L3" s="25" t="n"/>
-      <c r="M3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -25456,32 +24802,27 @@
       </c>
       <c r="H4" s="26" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="J4" s="26" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="K4" s="26" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="L4" s="26" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="M4" s="26" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
+          <t>Issue ID</t>
         </is>
       </c>
     </row>
@@ -25521,16 +24862,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr"/>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="28" t="n"/>
-      <c r="M5" s="12" t="n"/>
+      <c r="K5" s="28" t="n"/>
+      <c r="L5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -25568,16 +24908,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr"/>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="H6" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="28" t="n"/>
-      <c r="M6" s="12" t="n"/>
+      <c r="K6" s="28" t="n"/>
+      <c r="L6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -25615,16 +24954,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr"/>
-      <c r="I7" s="27" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="28" t="n"/>
-      <c r="M7" s="12" t="n"/>
+      <c r="K7" s="28" t="n"/>
+      <c r="L7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -25662,16 +25000,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr"/>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="H8" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="28" t="n"/>
-      <c r="M8" s="12" t="n"/>
+      <c r="K8" s="28" t="n"/>
+      <c r="L8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -25709,16 +25046,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr"/>
-      <c r="I9" s="27" t="inlineStr">
+      <c r="H9" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I9" s="12" t="n"/>
       <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="28" t="n"/>
-      <c r="M9" s="12" t="n"/>
+      <c r="K9" s="28" t="n"/>
+      <c r="L9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -25756,16 +25092,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="27" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="28" t="n"/>
-      <c r="M10" s="12" t="n"/>
+      <c r="K10" s="28" t="n"/>
+      <c r="L10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -25800,19 +25135,18 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Data Migration is not in the menu; GET /api/v1/migration/objects returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="27" t="inlineStr">
+          <t>Data Migration is not in the menu; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="28" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="K11" s="28" t="n"/>
+      <c r="L11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -25847,19 +25181,18 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Data Migration is not in the menu; GET /api/v1/migration/objects returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr"/>
-      <c r="I12" s="27" t="inlineStr">
+          <t>Data Migration is not in the menu; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="28" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -25894,19 +25227,18 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Data Migration is not in the menu; GET /api/v1/migration/objects returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="27" t="inlineStr">
+          <t>Data Migration is not in the menu; a direct request is refused.</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I13" s="12" t="n"/>
       <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="28" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="K13" s="28" t="n"/>
+      <c r="L13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -25944,16 +25276,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="H14" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I14" s="12" t="n"/>
       <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="28" t="n"/>
-      <c r="M14" s="12" t="n"/>
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -25988,19 +25319,18 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>New Object and Submit Decision are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="27" t="inlineStr">
+          <t>New Object and Submit Decision are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H15" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="28" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="K15" s="28" t="n"/>
+      <c r="L15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -26035,19 +25365,18 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>New Object and Submit Decision are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr"/>
-      <c r="I16" s="27" t="inlineStr">
+          <t>New Object and Submit Decision are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H16" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="28" t="n"/>
-      <c r="M16" s="12" t="n"/>
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -26082,19 +25411,18 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>New Object and Submit Decision are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="27" t="inlineStr">
+          <t>New Object and Submit Decision are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H17" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I17" s="12" t="n"/>
       <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="28" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -26132,16 +25460,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr"/>
-      <c r="I18" s="27" t="inlineStr">
+      <c r="H18" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I18" s="12" t="n"/>
       <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="28" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -26176,19 +25503,18 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>The item is not offered in My Approvals; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr"/>
-      <c r="I19" s="27" t="inlineStr">
+          <t>The item is not offered in My Approvals; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H19" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I19" s="12" t="n"/>
       <c r="J19" s="12" t="n"/>
-      <c r="K19" s="12" t="n"/>
-      <c r="L19" s="28" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="K19" s="28" t="n"/>
+      <c r="L19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -26223,19 +25549,18 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>The item is not offered in My Approvals; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr"/>
-      <c r="I20" s="27" t="inlineStr">
+          <t>The item is not offered in My Approvals; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H20" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="28" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="K20" s="28" t="n"/>
+      <c r="L20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -26270,19 +25595,18 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>The item is not offered in My Approvals; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr"/>
-      <c r="I21" s="27" t="inlineStr">
+          <t>The item is not offered in My Approvals; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H21" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I21" s="12" t="n"/>
       <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="28" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="K21" s="28" t="n"/>
+      <c r="L21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -26320,16 +25644,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H22" s="12" t="inlineStr"/>
-      <c r="I22" s="27" t="inlineStr">
+      <c r="H22" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I22" s="12" t="n"/>
       <c r="J22" s="12" t="n"/>
-      <c r="K22" s="12" t="n"/>
-      <c r="L22" s="28" t="n"/>
-      <c r="M22" s="12" t="n"/>
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -26364,19 +25687,18 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>The maps are read only; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="27" t="inlineStr">
+          <t>The maps are read only; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H23" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I23" s="12" t="n"/>
       <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="28" t="n"/>
-      <c r="M23" s="12" t="n"/>
+      <c r="K23" s="28" t="n"/>
+      <c r="L23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -26411,19 +25733,18 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>The maps are read only; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr"/>
-      <c r="I24" s="27" t="inlineStr">
+          <t>The maps are read only; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H24" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I24" s="12" t="n"/>
       <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="28" t="n"/>
-      <c r="M24" s="12" t="n"/>
+      <c r="K24" s="28" t="n"/>
+      <c r="L24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -26461,16 +25782,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr"/>
-      <c r="I25" s="27" t="inlineStr">
+      <c r="H25" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I25" s="12" t="n"/>
       <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="28" t="n"/>
-      <c r="M25" s="12" t="n"/>
+      <c r="K25" s="28" t="n"/>
+      <c r="L25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -26505,19 +25825,18 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Upload and Load are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr"/>
-      <c r="I26" s="27" t="inlineStr">
+          <t>Upload and Load are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H26" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I26" s="12" t="n"/>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="28" t="n"/>
-      <c r="M26" s="12" t="n"/>
+      <c r="K26" s="28" t="n"/>
+      <c r="L26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -26552,19 +25871,18 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Upload and Load are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr"/>
-      <c r="I27" s="27" t="inlineStr">
+          <t>Upload and Load are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H27" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I27" s="12" t="n"/>
       <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="28" t="n"/>
-      <c r="M27" s="12" t="n"/>
+      <c r="K27" s="28" t="n"/>
+      <c r="L27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -26599,19 +25917,18 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>Upload and Load are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="inlineStr"/>
-      <c r="I28" s="27" t="inlineStr">
+          <t>Upload and Load are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H28" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I28" s="12" t="n"/>
       <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="28" t="n"/>
-      <c r="M28" s="12" t="n"/>
+      <c r="K28" s="28" t="n"/>
+      <c r="L28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -26649,16 +25966,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr"/>
-      <c r="I29" s="27" t="inlineStr">
+      <c r="H29" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I29" s="12" t="n"/>
       <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="28" t="n"/>
-      <c r="M29" s="12" t="n"/>
+      <c r="K29" s="28" t="n"/>
+      <c r="L29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -26693,19 +26009,18 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>Approve Load is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr"/>
-      <c r="I30" s="27" t="inlineStr">
+          <t>Approve Load is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H30" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I30" s="12" t="n"/>
       <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="28" t="n"/>
-      <c r="M30" s="12" t="n"/>
+      <c r="K30" s="28" t="n"/>
+      <c r="L30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -26740,19 +26055,18 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Approve Load is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="inlineStr"/>
-      <c r="I31" s="27" t="inlineStr">
+          <t>Approve Load is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I31" s="12" t="n"/>
       <c r="J31" s="12" t="n"/>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="28" t="n"/>
-      <c r="M31" s="12" t="n"/>
+      <c r="K31" s="28" t="n"/>
+      <c r="L31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -26790,16 +26104,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr"/>
-      <c r="I32" s="27" t="inlineStr">
+      <c r="H32" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I32" s="12" t="n"/>
       <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="28" t="n"/>
-      <c r="M32" s="12" t="n"/>
+      <c r="K32" s="28" t="n"/>
+      <c r="L32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -26834,19 +26147,18 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Sign and Approve are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="inlineStr"/>
-      <c r="I33" s="27" t="inlineStr">
+          <t>Sign and Approve are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H33" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I33" s="12" t="n"/>
       <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="28" t="n"/>
-      <c r="M33" s="12" t="n"/>
+      <c r="K33" s="28" t="n"/>
+      <c r="L33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -26881,19 +26193,18 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>Sign and Approve are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr"/>
-      <c r="I34" s="27" t="inlineStr">
+          <t>Sign and Approve are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H34" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I34" s="12" t="n"/>
       <c r="J34" s="12" t="n"/>
-      <c r="K34" s="12" t="n"/>
-      <c r="L34" s="28" t="n"/>
-      <c r="M34" s="12" t="n"/>
+      <c r="K34" s="28" t="n"/>
+      <c r="L34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -26928,19 +26239,18 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Sign and Approve are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr"/>
-      <c r="I35" s="27" t="inlineStr">
+          <t>Sign and Approve are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H35" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I35" s="12" t="n"/>
       <c r="J35" s="12" t="n"/>
-      <c r="K35" s="12" t="n"/>
-      <c r="L35" s="28" t="n"/>
-      <c r="M35" s="12" t="n"/>
+      <c r="K35" s="28" t="n"/>
+      <c r="L35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -26978,16 +26288,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr"/>
-      <c r="I36" s="27" t="inlineStr">
+      <c r="H36" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I36" s="12" t="n"/>
       <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
-      <c r="L36" s="28" t="n"/>
-      <c r="M36" s="12" t="n"/>
+      <c r="K36" s="28" t="n"/>
+      <c r="L36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -27022,19 +26331,18 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>GO and NO-GO are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr"/>
-      <c r="I37" s="27" t="inlineStr">
+          <t>GO and NO-GO are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H37" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I37" s="12" t="n"/>
       <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
-      <c r="L37" s="28" t="n"/>
-      <c r="M37" s="12" t="n"/>
+      <c r="K37" s="28" t="n"/>
+      <c r="L37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -27069,19 +26377,18 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>GO and NO-GO are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr"/>
-      <c r="I38" s="27" t="inlineStr">
+          <t>GO and NO-GO are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H38" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I38" s="12" t="n"/>
       <c r="J38" s="12" t="n"/>
-      <c r="K38" s="12" t="n"/>
-      <c r="L38" s="28" t="n"/>
-      <c r="M38" s="12" t="n"/>
+      <c r="K38" s="28" t="n"/>
+      <c r="L38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -27119,16 +26426,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr"/>
-      <c r="I39" s="27" t="inlineStr">
+      <c r="H39" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I39" s="12" t="n"/>
       <c r="J39" s="12" t="n"/>
-      <c r="K39" s="12" t="n"/>
-      <c r="L39" s="28" t="n"/>
-      <c r="M39" s="12" t="n"/>
+      <c r="K39" s="28" t="n"/>
+      <c r="L39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -27163,19 +26469,18 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>Legacy Inquiry is not in the menu; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="inlineStr"/>
-      <c r="I40" s="27" t="inlineStr">
+          <t>Legacy Inquiry is not in the menu; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H40" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I40" s="12" t="n"/>
       <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
-      <c r="L40" s="28" t="n"/>
-      <c r="M40" s="12" t="n"/>
+      <c r="K40" s="28" t="n"/>
+      <c r="L40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -27210,19 +26515,18 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>Legacy Inquiry is not in the menu; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr"/>
-      <c r="I41" s="27" t="inlineStr">
+          <t>Legacy Inquiry is not in the menu; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H41" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I41" s="12" t="n"/>
       <c r="J41" s="12" t="n"/>
-      <c r="K41" s="12" t="n"/>
-      <c r="L41" s="28" t="n"/>
-      <c r="M41" s="12" t="n"/>
+      <c r="K41" s="28" t="n"/>
+      <c r="L41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -27260,16 +26564,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr"/>
-      <c r="I42" s="27" t="inlineStr">
+      <c r="H42" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I42" s="12" t="n"/>
       <c r="J42" s="12" t="n"/>
-      <c r="K42" s="12" t="n"/>
-      <c r="L42" s="28" t="n"/>
-      <c r="M42" s="12" t="n"/>
+      <c r="K42" s="28" t="n"/>
+      <c r="L42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -27304,19 +26607,18 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>Access Log is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr"/>
-      <c r="I43" s="27" t="inlineStr">
+          <t>Access Log is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H43" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I43" s="12" t="n"/>
       <c r="J43" s="12" t="n"/>
-      <c r="K43" s="12" t="n"/>
-      <c r="L43" s="28" t="n"/>
-      <c r="M43" s="12" t="n"/>
+      <c r="K43" s="28" t="n"/>
+      <c r="L43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -27351,19 +26653,18 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>Access Log is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr"/>
-      <c r="I44" s="27" t="inlineStr">
+          <t>Access Log is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I44" s="12" t="n"/>
       <c r="J44" s="12" t="n"/>
-      <c r="K44" s="12" t="n"/>
-      <c r="L44" s="28" t="n"/>
-      <c r="M44" s="12" t="n"/>
+      <c r="K44" s="28" t="n"/>
+      <c r="L44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -27401,16 +26702,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H45" s="12" t="inlineStr"/>
-      <c r="I45" s="27" t="inlineStr">
+      <c r="H45" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I45" s="12" t="n"/>
       <c r="J45" s="12" t="n"/>
-      <c r="K45" s="12" t="n"/>
-      <c r="L45" s="28" t="n"/>
-      <c r="M45" s="12" t="n"/>
+      <c r="K45" s="28" t="n"/>
+      <c r="L45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -27445,19 +26745,18 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>The batch is not offered at the top-management stage; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr"/>
-      <c r="I46" s="27" t="inlineStr">
+          <t>The batch is not offered at the top-management stage; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H46" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I46" s="12" t="n"/>
       <c r="J46" s="12" t="n"/>
-      <c r="K46" s="12" t="n"/>
-      <c r="L46" s="28" t="n"/>
-      <c r="M46" s="12" t="n"/>
+      <c r="K46" s="28" t="n"/>
+      <c r="L46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -27492,19 +26791,18 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>The batch is not offered at the top-management stage; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr"/>
-      <c r="I47" s="27" t="inlineStr">
+          <t>The batch is not offered at the top-management stage; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H47" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I47" s="12" t="n"/>
       <c r="J47" s="12" t="n"/>
-      <c r="K47" s="12" t="n"/>
-      <c r="L47" s="28" t="n"/>
-      <c r="M47" s="12" t="n"/>
+      <c r="K47" s="28" t="n"/>
+      <c r="L47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -27542,16 +26840,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H48" s="12" t="inlineStr"/>
-      <c r="I48" s="27" t="inlineStr">
+      <c r="H48" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I48" s="12" t="n"/>
       <c r="J48" s="12" t="n"/>
-      <c r="K48" s="12" t="n"/>
-      <c r="L48" s="28" t="n"/>
-      <c r="M48" s="12" t="n"/>
+      <c r="K48" s="28" t="n"/>
+      <c r="L48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -27589,16 +26886,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr"/>
-      <c r="I49" s="27" t="inlineStr">
+      <c r="H49" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I49" s="12" t="n"/>
       <c r="J49" s="12" t="n"/>
-      <c r="K49" s="12" t="n"/>
-      <c r="L49" s="28" t="n"/>
-      <c r="M49" s="12" t="n"/>
+      <c r="K49" s="28" t="n"/>
+      <c r="L49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -27633,19 +26929,18 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>Approve is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr"/>
-      <c r="I50" s="27" t="inlineStr">
+          <t>Approve is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H50" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I50" s="12" t="n"/>
       <c r="J50" s="12" t="n"/>
-      <c r="K50" s="12" t="n"/>
-      <c r="L50" s="28" t="n"/>
-      <c r="M50" s="12" t="n"/>
+      <c r="K50" s="28" t="n"/>
+      <c r="L50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -27680,19 +26975,18 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>Approve is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr"/>
-      <c r="I51" s="27" t="inlineStr">
+          <t>Approve is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H51" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I51" s="12" t="n"/>
       <c r="J51" s="12" t="n"/>
-      <c r="K51" s="12" t="n"/>
-      <c r="L51" s="28" t="n"/>
-      <c r="M51" s="12" t="n"/>
+      <c r="K51" s="28" t="n"/>
+      <c r="L51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -27730,16 +27024,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr"/>
-      <c r="I52" s="27" t="inlineStr">
+      <c r="H52" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I52" s="12" t="n"/>
       <c r="J52" s="12" t="n"/>
-      <c r="K52" s="12" t="n"/>
-      <c r="L52" s="28" t="n"/>
-      <c r="M52" s="12" t="n"/>
+      <c r="K52" s="28" t="n"/>
+      <c r="L52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -27774,19 +27067,18 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>Submit is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H53" s="12" t="inlineStr"/>
-      <c r="I53" s="27" t="inlineStr">
+          <t>Submit is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H53" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I53" s="12" t="n"/>
       <c r="J53" s="12" t="n"/>
-      <c r="K53" s="12" t="n"/>
-      <c r="L53" s="28" t="n"/>
-      <c r="M53" s="12" t="n"/>
+      <c r="K53" s="28" t="n"/>
+      <c r="L53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -27821,19 +27113,18 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>Submit is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H54" s="12" t="inlineStr"/>
-      <c r="I54" s="27" t="inlineStr">
+          <t>Submit is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H54" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I54" s="12" t="n"/>
       <c r="J54" s="12" t="n"/>
-      <c r="K54" s="12" t="n"/>
-      <c r="L54" s="28" t="n"/>
-      <c r="M54" s="12" t="n"/>
+      <c r="K54" s="28" t="n"/>
+      <c r="L54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -27871,16 +27162,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H55" s="12" t="inlineStr"/>
-      <c r="I55" s="27" t="inlineStr">
+      <c r="H55" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I55" s="12" t="n"/>
       <c r="J55" s="12" t="n"/>
-      <c r="K55" s="12" t="n"/>
-      <c r="L55" s="28" t="n"/>
-      <c r="M55" s="12" t="n"/>
+      <c r="K55" s="28" t="n"/>
+      <c r="L55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -27915,19 +27205,18 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>The true-up is not offered in My Approvals; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H56" s="12" t="inlineStr"/>
-      <c r="I56" s="27" t="inlineStr">
+          <t>The true-up is not offered in My Approvals; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H56" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I56" s="12" t="n"/>
       <c r="J56" s="12" t="n"/>
-      <c r="K56" s="12" t="n"/>
-      <c r="L56" s="28" t="n"/>
-      <c r="M56" s="12" t="n"/>
+      <c r="K56" s="28" t="n"/>
+      <c r="L56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -27962,19 +27251,18 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>The true-up is not offered in My Approvals; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H57" s="12" t="inlineStr"/>
-      <c r="I57" s="27" t="inlineStr">
+          <t>The true-up is not offered in My Approvals; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H57" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I57" s="12" t="n"/>
       <c r="J57" s="12" t="n"/>
-      <c r="K57" s="12" t="n"/>
-      <c r="L57" s="28" t="n"/>
-      <c r="M57" s="12" t="n"/>
+      <c r="K57" s="28" t="n"/>
+      <c r="L57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -28012,16 +27300,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H58" s="12" t="inlineStr"/>
-      <c r="I58" s="27" t="inlineStr">
+      <c r="H58" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I58" s="12" t="n"/>
       <c r="J58" s="12" t="n"/>
-      <c r="K58" s="12" t="n"/>
-      <c r="L58" s="28" t="n"/>
-      <c r="M58" s="12" t="n"/>
+      <c r="K58" s="28" t="n"/>
+      <c r="L58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -28056,19 +27343,18 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>Approve is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H59" s="12" t="inlineStr"/>
-      <c r="I59" s="27" t="inlineStr">
+          <t>Approve is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H59" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I59" s="12" t="n"/>
       <c r="J59" s="12" t="n"/>
-      <c r="K59" s="12" t="n"/>
-      <c r="L59" s="28" t="n"/>
-      <c r="M59" s="12" t="n"/>
+      <c r="K59" s="28" t="n"/>
+      <c r="L59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -28103,26 +27389,25 @@
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>Approve is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H60" s="12" t="inlineStr"/>
-      <c r="I60" s="27" t="inlineStr">
+          <t>Approve is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H60" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I60" s="12" t="n"/>
       <c r="J60" s="12" t="n"/>
-      <c r="K60" s="12" t="n"/>
-      <c r="L60" s="28" t="n"/>
-      <c r="M60" s="12" t="n"/>
+      <c r="K60" s="28" t="n"/>
+      <c r="L60" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M60"/>
+  <autoFilter ref="A4:L60"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I560">
+  <conditionalFormatting sqref="H5:H560">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -28136,7 +27421,7 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:M560">
+  <conditionalFormatting sqref="A5:L560">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -28145,7 +27430,7 @@
     <dataValidation sqref="F5:F560" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Access" error="Choose a value from the list (Access)." type="list">
       <formula1>'_lists'!$F$1:$F$2</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I560" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="H5:H560" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$G$1:$G$5</formula1>
     </dataValidation>
   </dataValidations>
